--- a/Assets/ExcelData/ItemTable.xlsx
+++ b/Assets/ExcelData/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE404B3F-18A5-4D8F-8CA4-14DAF0ADE0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1129889-43C1-40A5-9BF3-394CAAE9F820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -37,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="219">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -803,6 +825,26 @@
   </si>
   <si>
     <t>HP 회복 포션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uncommon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1190,19 +1232,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506FB7A7-E3CC-4169-944D-8712D18417BF}">
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="44.25" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="13.625" customWidth="1"/>
-    <col min="6" max="6" width="15.375" customWidth="1"/>
-    <col min="9" max="9" width="12.75" customWidth="1"/>
-    <col min="10" max="10" width="28.125" customWidth="1"/>
+    <col min="2" max="2" width="32.75" customWidth="1"/>
+    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="13.625" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="10" max="10" width="12.75" customWidth="1"/>
+    <col min="11" max="11" width="28.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,50 +1253,54 @@
         <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>10000</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f>"Equipment_Icon_" &amp; D2 &amp; "_" &amp; "Tier" &amp; E2</f>
+        <f>"Equipment_Icon_" &amp; E2 &amp; "_" &amp; "Tier" &amp; F2</f>
         <v>Equipment_Icon_Hat_Tier1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="1" t="str" cm="1">
+        <f t="array" ref="C2">_xlfn.IFS(F2&lt;=2, "Common", F2&lt;=4, "Uncommon", F2&lt;=6, "Rare", F2&lt;=8, "Epic", F2=9, "Legendary", F2&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
@@ -1263,30 +1310,34 @@
       <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>10001</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f t="shared" ref="B3:B66" si="0">"Equipment_Icon_" &amp; D3 &amp; "_" &amp; "Tier" &amp; E3</f>
+        <f t="shared" ref="B3:B66" si="0">"Equipment_Icon_" &amp; E3 &amp; "_" &amp; "Tier" &amp; F3</f>
         <v>Equipment_Icon_Hat_Tier2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="1" t="str" cm="1">
+        <f t="array" ref="C3">_xlfn.IFS(F3&lt;=2, "Common", F3&lt;=4, "Uncommon", F3&lt;=6, "Rare", F3&lt;=8, "Epic", F3=9, "Legendary", F3&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
@@ -1296,11 +1347,14 @@
       <c r="I3" s="1">
         <v>0</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>10002</v>
       </c>
@@ -1308,18 +1362,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hat_Tier3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="1" t="str" cm="1">
+        <f t="array" ref="C4">_xlfn.IFS(F4&lt;=2, "Common", F4&lt;=4, "Uncommon", F4&lt;=6, "Rare", F4&lt;=8, "Epic", F4=9, "Legendary", F4&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>3</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
@@ -1329,11 +1384,14 @@
       <c r="I4" s="1">
         <v>0</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>10003</v>
       </c>
@@ -1341,18 +1399,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hat_Tier4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="1" t="str" cm="1">
+        <f t="array" ref="C5">_xlfn.IFS(F5&lt;=2, "Common", F5&lt;=4, "Uncommon", F5&lt;=6, "Rare", F5&lt;=8, "Epic", F5=9, "Legendary", F5&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
@@ -1362,11 +1421,14 @@
       <c r="I5" s="1">
         <v>0</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>10004</v>
       </c>
@@ -1374,18 +1436,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hat_Tier5</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="1" t="str" cm="1">
+        <f t="array" ref="C6">_xlfn.IFS(F6&lt;=2, "Common", F6&lt;=4, "Uncommon", F6&lt;=6, "Rare", F6&lt;=8, "Epic", F6=9, "Legendary", F6&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>5</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
@@ -1395,11 +1458,14 @@
       <c r="I6" s="1">
         <v>0</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>10005</v>
       </c>
@@ -1407,18 +1473,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hat_Tier6</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="1" t="str" cm="1">
+        <f t="array" ref="C7">_xlfn.IFS(F7&lt;=2, "Common", F7&lt;=4, "Uncommon", F7&lt;=6, "Rare", F7&lt;=8, "Epic", F7=9, "Legendary", F7&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
@@ -1428,11 +1495,14 @@
       <c r="I7" s="1">
         <v>0</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>10006</v>
       </c>
@@ -1440,18 +1510,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hat_Tier7</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="1" t="str" cm="1">
+        <f t="array" ref="C8">_xlfn.IFS(F8&lt;=2, "Common", F8&lt;=4, "Uncommon", F8&lt;=6, "Rare", F8&lt;=8, "Epic", F8=9, "Legendary", F8&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>7</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
@@ -1461,11 +1532,14 @@
       <c r="I8" s="1">
         <v>0</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>10007</v>
       </c>
@@ -1473,18 +1547,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hat_Tier8</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="1" t="str" cm="1">
+        <f t="array" ref="C9">_xlfn.IFS(F9&lt;=2, "Common", F9&lt;=4, "Uncommon", F9&lt;=6, "Rare", F9&lt;=8, "Epic", F9=9, "Legendary", F9&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>8</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
@@ -1494,11 +1569,14 @@
       <c r="I9" s="1">
         <v>0</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>10008</v>
       </c>
@@ -1506,18 +1584,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hat_Tier9</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="1" t="str" cm="1">
+        <f t="array" ref="C10">_xlfn.IFS(F10&lt;=2, "Common", F10&lt;=4, "Uncommon", F10&lt;=6, "Rare", F10&lt;=8, "Epic", F10=9, "Legendary", F10&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>9</v>
       </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
@@ -1527,11 +1606,14 @@
       <c r="I10" s="1">
         <v>0</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10009</v>
       </c>
@@ -1539,18 +1621,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hat_Tier10</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="1" t="str" cm="1">
+        <f t="array" ref="C11">_xlfn.IFS(F11&lt;=2, "Common", F11&lt;=4, "Uncommon", F11&lt;=6, "Rare", F11&lt;=8, "Epic", F11=9, "Legendary", F11&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>10</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
@@ -1560,11 +1643,14 @@
       <c r="I11" s="1">
         <v>0</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10010</v>
       </c>
@@ -1572,18 +1658,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier1</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="1" t="str" cm="1">
+        <f t="array" ref="C12">_xlfn.IFS(F12&lt;=2, "Common", F12&lt;=4, "Uncommon", F12&lt;=6, "Rare", F12&lt;=8, "Epic", F12=9, "Legendary", F12&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
@@ -1593,11 +1680,14 @@
       <c r="I12" s="1">
         <v>0</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10011</v>
       </c>
@@ -1605,18 +1695,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier2</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="1" t="str" cm="1">
+        <f t="array" ref="C13">_xlfn.IFS(F13&lt;=2, "Common", F13&lt;=4, "Uncommon", F13&lt;=6, "Rare", F13&lt;=8, "Epic", F13=9, "Legendary", F13&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
@@ -1626,11 +1717,14 @@
       <c r="I13" s="1">
         <v>0</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10012</v>
       </c>
@@ -1638,18 +1732,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier3</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="1" t="str" cm="1">
+        <f t="array" ref="C14">_xlfn.IFS(F14&lt;=2, "Common", F14&lt;=4, "Uncommon", F14&lt;=6, "Rare", F14&lt;=8, "Epic", F14=9, "Legendary", F14&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>3</v>
       </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
@@ -1659,11 +1754,14 @@
       <c r="I14" s="1">
         <v>0</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>10013</v>
       </c>
@@ -1671,18 +1769,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier4</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="1" t="str" cm="1">
+        <f t="array" ref="C15">_xlfn.IFS(F15&lt;=2, "Common", F15&lt;=4, "Uncommon", F15&lt;=6, "Rare", F15&lt;=8, "Epic", F15=9, "Legendary", F15&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>4</v>
       </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
@@ -1692,11 +1791,14 @@
       <c r="I15" s="1">
         <v>0</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>10014</v>
       </c>
@@ -1704,18 +1806,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier5</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="1" t="str" cm="1">
+        <f t="array" ref="C16">_xlfn.IFS(F16&lt;=2, "Common", F16&lt;=4, "Uncommon", F16&lt;=6, "Rare", F16&lt;=8, "Epic", F16=9, "Legendary", F16&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>5</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
@@ -1725,11 +1828,14 @@
       <c r="I16" s="1">
         <v>0</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>10015</v>
       </c>
@@ -1737,18 +1843,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier6</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="1" t="str" cm="1">
+        <f t="array" ref="C17">_xlfn.IFS(F17&lt;=2, "Common", F17&lt;=4, "Uncommon", F17&lt;=6, "Rare", F17&lt;=8, "Epic", F17=9, "Legendary", F17&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
@@ -1758,11 +1865,14 @@
       <c r="I17" s="1">
         <v>0</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>10016</v>
       </c>
@@ -1770,18 +1880,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier7</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="1" t="str" cm="1">
+        <f t="array" ref="C18">_xlfn.IFS(F18&lt;=2, "Common", F18&lt;=4, "Uncommon", F18&lt;=6, "Rare", F18&lt;=8, "Epic", F18=9, "Legendary", F18&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>7</v>
       </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
@@ -1791,11 +1902,14 @@
       <c r="I18" s="1">
         <v>0</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>10017</v>
       </c>
@@ -1803,18 +1917,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier8</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="1" t="str" cm="1">
+        <f t="array" ref="C19">_xlfn.IFS(F19&lt;=2, "Common", F19&lt;=4, "Uncommon", F19&lt;=6, "Rare", F19&lt;=8, "Epic", F19=9, "Legendary", F19&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>8</v>
       </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
@@ -1824,11 +1939,14 @@
       <c r="I19" s="1">
         <v>0</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>10018</v>
       </c>
@@ -1836,18 +1954,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier9</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="1" t="str" cm="1">
+        <f t="array" ref="C20">_xlfn.IFS(F20&lt;=2, "Common", F20&lt;=4, "Uncommon", F20&lt;=6, "Rare", F20&lt;=8, "Epic", F20=9, "Legendary", F20&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>9</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
@@ -1857,11 +1976,14 @@
       <c r="I20" s="1">
         <v>0</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>10019</v>
       </c>
@@ -1869,18 +1991,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Glove_Tier10</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="1" t="str" cm="1">
+        <f t="array" ref="C21">_xlfn.IFS(F21&lt;=2, "Common", F21&lt;=4, "Uncommon", F21&lt;=6, "Rare", F21&lt;=8, "Epic", F21=9, "Legendary", F21&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>10</v>
       </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
@@ -1890,11 +2013,14 @@
       <c r="I21" s="1">
         <v>0</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>10020</v>
       </c>
@@ -1902,18 +2028,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="1" t="str" cm="1">
+        <f t="array" ref="C22">_xlfn.IFS(F22&lt;=2, "Common", F22&lt;=4, "Uncommon", F22&lt;=6, "Rare", F22&lt;=8, "Epic", F22=9, "Legendary", F22&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
@@ -1923,11 +2050,14 @@
       <c r="I22" s="1">
         <v>0</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>10021</v>
       </c>
@@ -1935,18 +2065,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier2</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="1" t="str" cm="1">
+        <f t="array" ref="C23">_xlfn.IFS(F23&lt;=2, "Common", F23&lt;=4, "Uncommon", F23&lt;=6, "Rare", F23&lt;=8, "Epic", F23=9, "Legendary", F23&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
@@ -1956,11 +2087,14 @@
       <c r="I23" s="1">
         <v>0</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>10022</v>
       </c>
@@ -1968,18 +2102,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier3</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="1" t="str" cm="1">
+        <f t="array" ref="C24">_xlfn.IFS(F24&lt;=2, "Common", F24&lt;=4, "Uncommon", F24&lt;=6, "Rare", F24&lt;=8, "Epic", F24=9, "Legendary", F24&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>3</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
@@ -1989,11 +2124,14 @@
       <c r="I24" s="1">
         <v>0</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>10023</v>
       </c>
@@ -2001,18 +2139,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier4</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="1" t="str" cm="1">
+        <f t="array" ref="C25">_xlfn.IFS(F25&lt;=2, "Common", F25&lt;=4, "Uncommon", F25&lt;=6, "Rare", F25&lt;=8, "Epic", F25=9, "Legendary", F25&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>4</v>
       </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
@@ -2022,11 +2161,14 @@
       <c r="I25" s="1">
         <v>0</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>10024</v>
       </c>
@@ -2034,18 +2176,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="1" t="str" cm="1">
+        <f t="array" ref="C26">_xlfn.IFS(F26&lt;=2, "Common", F26&lt;=4, "Uncommon", F26&lt;=6, "Rare", F26&lt;=8, "Epic", F26=9, "Legendary", F26&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>5</v>
       </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
@@ -2055,11 +2198,14 @@
       <c r="I26" s="1">
         <v>0</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>10025</v>
       </c>
@@ -2067,18 +2213,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier6</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="1" t="str" cm="1">
+        <f t="array" ref="C27">_xlfn.IFS(F27&lt;=2, "Common", F27&lt;=4, "Uncommon", F27&lt;=6, "Rare", F27&lt;=8, "Epic", F27=9, "Legendary", F27&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <v>6</v>
       </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
@@ -2088,11 +2235,14 @@
       <c r="I27" s="1">
         <v>0</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>10026</v>
       </c>
@@ -2100,18 +2250,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier7</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="1" t="str" cm="1">
+        <f t="array" ref="C28">_xlfn.IFS(F28&lt;=2, "Common", F28&lt;=4, "Uncommon", F28&lt;=6, "Rare", F28&lt;=8, "Epic", F28=9, "Legendary", F28&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <v>7</v>
       </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
@@ -2121,11 +2272,14 @@
       <c r="I28" s="1">
         <v>0</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>10027</v>
       </c>
@@ -2133,18 +2287,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier8</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="1" t="str" cm="1">
+        <f t="array" ref="C29">_xlfn.IFS(F29&lt;=2, "Common", F29&lt;=4, "Uncommon", F29&lt;=6, "Rare", F29&lt;=8, "Epic", F29=9, "Legendary", F29&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>8</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
@@ -2154,11 +2309,14 @@
       <c r="I29" s="1">
         <v>0</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>10028</v>
       </c>
@@ -2166,18 +2324,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier9</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="1" t="str" cm="1">
+        <f t="array" ref="C30">_xlfn.IFS(F30&lt;=2, "Common", F30&lt;=4, "Uncommon", F30&lt;=6, "Rare", F30&lt;=8, "Epic", F30=9, "Legendary", F30&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="1">
+      <c r="F30" s="1">
         <v>9</v>
       </c>
-      <c r="F30" s="1">
-        <v>0</v>
-      </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
@@ -2187,11 +2346,14 @@
       <c r="I30" s="1">
         <v>0</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>10029</v>
       </c>
@@ -2199,18 +2361,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Shoes_Tier10</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="1" t="str" cm="1">
+        <f t="array" ref="C31">_xlfn.IFS(F31&lt;=2, "Common", F31&lt;=4, "Uncommon", F31&lt;=6, "Rare", F31&lt;=8, "Epic", F31=9, "Legendary", F31&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="1">
+      <c r="F31" s="1">
         <v>10</v>
       </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
@@ -2220,11 +2383,14 @@
       <c r="I31" s="1">
         <v>0</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>10030</v>
       </c>
@@ -2232,18 +2398,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier1</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="1" t="str" cm="1">
+        <f t="array" ref="C32">_xlfn.IFS(F32&lt;=2, "Common", F32&lt;=4, "Uncommon", F32&lt;=6, "Rare", F32&lt;=8, "Epic", F32=9, "Legendary", F32&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="1">
+      <c r="F32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
@@ -2253,11 +2420,14 @@
       <c r="I32" s="1">
         <v>0</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>10031</v>
       </c>
@@ -2265,18 +2435,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier2</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="1" t="str" cm="1">
+        <f t="array" ref="C33">_xlfn.IFS(F33&lt;=2, "Common", F33&lt;=4, "Uncommon", F33&lt;=6, "Rare", F33&lt;=8, "Epic", F33=9, "Legendary", F33&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="1">
+      <c r="F33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="1">
-        <v>0</v>
-      </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
@@ -2286,11 +2457,14 @@
       <c r="I33" s="1">
         <v>0</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>10032</v>
       </c>
@@ -2298,18 +2472,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier3</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="1" t="str" cm="1">
+        <f t="array" ref="C34">_xlfn.IFS(F34&lt;=2, "Common", F34&lt;=4, "Uncommon", F34&lt;=6, "Rare", F34&lt;=8, "Epic", F34=9, "Legendary", F34&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="1">
+      <c r="F34" s="1">
         <v>3</v>
       </c>
-      <c r="F34" s="1">
-        <v>0</v>
-      </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
@@ -2319,11 +2494,14 @@
       <c r="I34" s="1">
         <v>0</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>10033</v>
       </c>
@@ -2331,18 +2509,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier4</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="1" t="str" cm="1">
+        <f t="array" ref="C35">_xlfn.IFS(F35&lt;=2, "Common", F35&lt;=4, "Uncommon", F35&lt;=6, "Rare", F35&lt;=8, "Epic", F35=9, "Legendary", F35&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="1">
+      <c r="F35" s="1">
         <v>4</v>
       </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
@@ -2352,11 +2531,14 @@
       <c r="I35" s="1">
         <v>0</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>10034</v>
       </c>
@@ -2364,18 +2546,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier5</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="1" t="str" cm="1">
+        <f t="array" ref="C36">_xlfn.IFS(F36&lt;=2, "Common", F36&lt;=4, "Uncommon", F36&lt;=6, "Rare", F36&lt;=8, "Epic", F36=9, "Legendary", F36&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E36" s="1">
+      <c r="F36" s="1">
         <v>5</v>
       </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
@@ -2385,11 +2568,14 @@
       <c r="I36" s="1">
         <v>0</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>10035</v>
       </c>
@@ -2397,18 +2583,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier6</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="1" t="str" cm="1">
+        <f t="array" ref="C37">_xlfn.IFS(F37&lt;=2, "Common", F37&lt;=4, "Uncommon", F37&lt;=6, "Rare", F37&lt;=8, "Epic", F37=9, "Legendary", F37&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E37" s="1">
+      <c r="F37" s="1">
         <v>6</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
       <c r="G37" s="1">
         <v>0</v>
       </c>
@@ -2418,11 +2605,14 @@
       <c r="I37" s="1">
         <v>0</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>10036</v>
       </c>
@@ -2430,18 +2620,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier7</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="1" t="str" cm="1">
+        <f t="array" ref="C38">_xlfn.IFS(F38&lt;=2, "Common", F38&lt;=4, "Uncommon", F38&lt;=6, "Rare", F38&lt;=8, "Epic", F38=9, "Legendary", F38&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E38" s="1">
+      <c r="F38" s="1">
         <v>7</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
       <c r="G38" s="1">
         <v>0</v>
       </c>
@@ -2451,11 +2642,14 @@
       <c r="I38" s="1">
         <v>0</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>10037</v>
       </c>
@@ -2463,18 +2657,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier8</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="1" t="str" cm="1">
+        <f t="array" ref="C39">_xlfn.IFS(F39&lt;=2, "Common", F39&lt;=4, "Uncommon", F39&lt;=6, "Rare", F39&lt;=8, "Epic", F39=9, "Legendary", F39&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="1">
+      <c r="F39" s="1">
         <v>8</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
       <c r="G39" s="1">
         <v>0</v>
       </c>
@@ -2484,11 +2679,14 @@
       <c r="I39" s="1">
         <v>0</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>10038</v>
       </c>
@@ -2496,18 +2694,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier9</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="1" t="str" cm="1">
+        <f t="array" ref="C40">_xlfn.IFS(F40&lt;=2, "Common", F40&lt;=4, "Uncommon", F40&lt;=6, "Rare", F40&lt;=8, "Epic", F40=9, "Legendary", F40&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E40" s="1">
+      <c r="F40" s="1">
         <v>9</v>
       </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
@@ -2517,11 +2716,14 @@
       <c r="I40" s="1">
         <v>0</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>10039</v>
       </c>
@@ -2529,18 +2731,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Badge_Tier10</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="1" t="str" cm="1">
+        <f t="array" ref="C41">_xlfn.IFS(F41&lt;=2, "Common", F41&lt;=4, "Uncommon", F41&lt;=6, "Rare", F41&lt;=8, "Epic", F41=9, "Legendary", F41&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E41" s="1">
+      <c r="F41" s="1">
         <v>10</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
@@ -2550,11 +2753,14 @@
       <c r="I41" s="1">
         <v>0</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>10040</v>
       </c>
@@ -2562,18 +2768,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier1</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="1" t="str" cm="1">
+        <f t="array" ref="C42">_xlfn.IFS(F42&lt;=2, "Common", F42&lt;=4, "Uncommon", F42&lt;=6, "Rare", F42&lt;=8, "Epic", F42=9, "Legendary", F42&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E42" s="1">
+      <c r="F42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
@@ -2583,11 +2790,14 @@
       <c r="I42" s="1">
         <v>0</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>10041</v>
       </c>
@@ -2595,18 +2805,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier2</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="1" t="str" cm="1">
+        <f t="array" ref="C43">_xlfn.IFS(F43&lt;=2, "Common", F43&lt;=4, "Uncommon", F43&lt;=6, "Rare", F43&lt;=8, "Epic", F43=9, "Legendary", F43&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E43" s="1">
+      <c r="F43" s="1">
         <v>2</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
       <c r="G43" s="1">
         <v>0</v>
       </c>
@@ -2616,11 +2827,14 @@
       <c r="I43" s="1">
         <v>0</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>10042</v>
       </c>
@@ -2628,18 +2842,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier3</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="1" t="str" cm="1">
+        <f t="array" ref="C44">_xlfn.IFS(F44&lt;=2, "Common", F44&lt;=4, "Uncommon", F44&lt;=6, "Rare", F44&lt;=8, "Epic", F44=9, "Legendary", F44&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="1">
+      <c r="F44" s="1">
         <v>3</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
       <c r="G44" s="1">
         <v>0</v>
       </c>
@@ -2649,11 +2864,14 @@
       <c r="I44" s="1">
         <v>0</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>10043</v>
       </c>
@@ -2661,18 +2879,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier4</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="1" t="str" cm="1">
+        <f t="array" ref="C45">_xlfn.IFS(F45&lt;=2, "Common", F45&lt;=4, "Uncommon", F45&lt;=6, "Rare", F45&lt;=8, "Epic", F45=9, "Legendary", F45&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E45" s="1">
+      <c r="F45" s="1">
         <v>4</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
@@ -2682,11 +2901,14 @@
       <c r="I45" s="1">
         <v>0</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>10044</v>
       </c>
@@ -2694,18 +2916,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier5</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="1" t="str" cm="1">
+        <f t="array" ref="C46">_xlfn.IFS(F46&lt;=2, "Common", F46&lt;=4, "Uncommon", F46&lt;=6, "Rare", F46&lt;=8, "Epic", F46=9, "Legendary", F46&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E46" s="1">
+      <c r="F46" s="1">
         <v>5</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
       <c r="G46" s="1">
         <v>0</v>
       </c>
@@ -2715,11 +2938,14 @@
       <c r="I46" s="1">
         <v>0</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>10045</v>
       </c>
@@ -2727,18 +2953,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier6</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="1" t="str" cm="1">
+        <f t="array" ref="C47">_xlfn.IFS(F47&lt;=2, "Common", F47&lt;=4, "Uncommon", F47&lt;=6, "Rare", F47&lt;=8, "Epic", F47=9, "Legendary", F47&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="1">
+      <c r="F47" s="1">
         <v>6</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
@@ -2748,11 +2975,14 @@
       <c r="I47" s="1">
         <v>0</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>10046</v>
       </c>
@@ -2760,18 +2990,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier7</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="1" t="str" cm="1">
+        <f t="array" ref="C48">_xlfn.IFS(F48&lt;=2, "Common", F48&lt;=4, "Uncommon", F48&lt;=6, "Rare", F48&lt;=8, "Epic", F48=9, "Legendary", F48&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E48" s="1">
+      <c r="F48" s="1">
         <v>7</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
@@ -2781,11 +3012,14 @@
       <c r="I48" s="1">
         <v>0</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>10047</v>
       </c>
@@ -2793,18 +3027,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier8</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="1" t="str" cm="1">
+        <f t="array" ref="C49">_xlfn.IFS(F49&lt;=2, "Common", F49&lt;=4, "Uncommon", F49&lt;=6, "Rare", F49&lt;=8, "Epic", F49=9, "Legendary", F49&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E49" s="1">
+      <c r="F49" s="1">
         <v>8</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
@@ -2814,11 +3049,14 @@
       <c r="I49" s="1">
         <v>0</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>10048</v>
       </c>
@@ -2826,18 +3064,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier9</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="1" t="str" cm="1">
+        <f t="array" ref="C50">_xlfn.IFS(F50&lt;=2, "Common", F50&lt;=4, "Uncommon", F50&lt;=6, "Rare", F50&lt;=8, "Epic", F50=9, "Legendary", F50&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E50" s="1">
+      <c r="F50" s="1">
         <v>9</v>
       </c>
-      <c r="F50" s="1">
-        <v>0</v>
-      </c>
       <c r="G50" s="1">
         <v>0</v>
       </c>
@@ -2847,11 +3086,14 @@
       <c r="I50" s="1">
         <v>0</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>10049</v>
       </c>
@@ -2859,18 +3101,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Bag_Tier10</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="1" t="str" cm="1">
+        <f t="array" ref="C51">_xlfn.IFS(F51&lt;=2, "Common", F51&lt;=4, "Uncommon", F51&lt;=6, "Rare", F51&lt;=8, "Epic", F51=9, "Legendary", F51&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E51" s="1">
+      <c r="F51" s="1">
         <v>10</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
       <c r="G51" s="1">
         <v>0</v>
       </c>
@@ -2880,11 +3123,14 @@
       <c r="I51" s="1">
         <v>0</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>10050</v>
       </c>
@@ -2892,18 +3138,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier1</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="1" t="str" cm="1">
+        <f t="array" ref="C52">_xlfn.IFS(F52&lt;=2, "Common", F52&lt;=4, "Uncommon", F52&lt;=6, "Rare", F52&lt;=8, "Epic", F52=9, "Legendary", F52&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E52" s="1">
+      <c r="F52" s="1">
         <v>1</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
@@ -2913,11 +3160,14 @@
       <c r="I52" s="1">
         <v>0</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>10051</v>
       </c>
@@ -2925,18 +3175,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier2</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="1" t="str" cm="1">
+        <f t="array" ref="C53">_xlfn.IFS(F53&lt;=2, "Common", F53&lt;=4, "Uncommon", F53&lt;=6, "Rare", F53&lt;=8, "Epic", F53=9, "Legendary", F53&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E53" s="1">
+      <c r="F53" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
@@ -2946,11 +3197,14 @@
       <c r="I53" s="1">
         <v>0</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>10052</v>
       </c>
@@ -2958,18 +3212,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier3</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="1" t="str" cm="1">
+        <f t="array" ref="C54">_xlfn.IFS(F54&lt;=2, "Common", F54&lt;=4, "Uncommon", F54&lt;=6, "Rare", F54&lt;=8, "Epic", F54=9, "Legendary", F54&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E54" s="1">
+      <c r="F54" s="1">
         <v>3</v>
       </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
       <c r="G54" s="1">
         <v>0</v>
       </c>
@@ -2979,11 +3234,14 @@
       <c r="I54" s="1">
         <v>0</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>10053</v>
       </c>
@@ -2991,18 +3249,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier4</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="1" t="str" cm="1">
+        <f t="array" ref="C55">_xlfn.IFS(F55&lt;=2, "Common", F55&lt;=4, "Uncommon", F55&lt;=6, "Rare", F55&lt;=8, "Epic", F55=9, "Legendary", F55&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E55" s="1">
+      <c r="F55" s="1">
         <v>4</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
@@ -3012,11 +3271,14 @@
       <c r="I55" s="1">
         <v>0</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>10054</v>
       </c>
@@ -3024,18 +3286,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier5</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="1" t="str" cm="1">
+        <f t="array" ref="C56">_xlfn.IFS(F56&lt;=2, "Common", F56&lt;=4, "Uncommon", F56&lt;=6, "Rare", F56&lt;=8, "Epic", F56=9, "Legendary", F56&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E56" s="1">
+      <c r="F56" s="1">
         <v>5</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
       <c r="G56" s="1">
         <v>0</v>
       </c>
@@ -3045,11 +3308,14 @@
       <c r="I56" s="1">
         <v>0</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>10055</v>
       </c>
@@ -3057,18 +3323,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier6</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="1" t="str" cm="1">
+        <f t="array" ref="C57">_xlfn.IFS(F57&lt;=2, "Common", F57&lt;=4, "Uncommon", F57&lt;=6, "Rare", F57&lt;=8, "Epic", F57=9, "Legendary", F57&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E57" s="1">
+      <c r="F57" s="1">
         <v>6</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
@@ -3078,11 +3345,14 @@
       <c r="I57" s="1">
         <v>0</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>10056</v>
       </c>
@@ -3090,18 +3360,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier7</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="1" t="str" cm="1">
+        <f t="array" ref="C58">_xlfn.IFS(F58&lt;=2, "Common", F58&lt;=4, "Uncommon", F58&lt;=6, "Rare", F58&lt;=8, "Epic", F58=9, "Legendary", F58&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E58" s="1">
+      <c r="F58" s="1">
         <v>7</v>
       </c>
-      <c r="F58" s="1">
-        <v>0</v>
-      </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
@@ -3111,11 +3382,14 @@
       <c r="I58" s="1">
         <v>0</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>10057</v>
       </c>
@@ -3123,18 +3397,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier8</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="1" t="str" cm="1">
+        <f t="array" ref="C59">_xlfn.IFS(F59&lt;=2, "Common", F59&lt;=4, "Uncommon", F59&lt;=6, "Rare", F59&lt;=8, "Epic", F59=9, "Legendary", F59&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E59" s="1">
+      <c r="F59" s="1">
         <v>8</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
       <c r="G59" s="1">
         <v>0</v>
       </c>
@@ -3144,11 +3419,14 @@
       <c r="I59" s="1">
         <v>0</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>10058</v>
       </c>
@@ -3156,18 +3434,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier9</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="1" t="str" cm="1">
+        <f t="array" ref="C60">_xlfn.IFS(F60&lt;=2, "Common", F60&lt;=4, "Uncommon", F60&lt;=6, "Rare", F60&lt;=8, "Epic", F60=9, "Legendary", F60&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E60" s="1">
+      <c r="F60" s="1">
         <v>9</v>
       </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
@@ -3177,11 +3456,14 @@
       <c r="I60" s="1">
         <v>0</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>10059</v>
       </c>
@@ -3189,18 +3471,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Hairpin_Tier10</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="1" t="str" cm="1">
+        <f t="array" ref="C61">_xlfn.IFS(F61&lt;=2, "Common", F61&lt;=4, "Uncommon", F61&lt;=6, "Rare", F61&lt;=8, "Epic", F61=9, "Legendary", F61&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E61" s="1">
+      <c r="F61" s="1">
         <v>10</v>
       </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
@@ -3210,11 +3493,14 @@
       <c r="I61" s="1">
         <v>0</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>10060</v>
       </c>
@@ -3222,18 +3508,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Necklace_Tier1</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="1" t="str" cm="1">
+        <f t="array" ref="C62">_xlfn.IFS(F62&lt;=2, "Common", F62&lt;=4, "Uncommon", F62&lt;=6, "Rare", F62&lt;=8, "Epic", F62=9, "Legendary", F62&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E62" s="1">
+      <c r="F62" s="1">
         <v>1</v>
       </c>
-      <c r="F62" s="1">
-        <v>0</v>
-      </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
@@ -3243,11 +3530,14 @@
       <c r="I62" s="1">
         <v>0</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>10061</v>
       </c>
@@ -3255,18 +3545,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Necklace_Tier2</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="1" t="str" cm="1">
+        <f t="array" ref="C63">_xlfn.IFS(F63&lt;=2, "Common", F63&lt;=4, "Uncommon", F63&lt;=6, "Rare", F63&lt;=8, "Epic", F63=9, "Legendary", F63&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E63" s="1">
+      <c r="F63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="1">
-        <v>0</v>
-      </c>
       <c r="G63" s="1">
         <v>0</v>
       </c>
@@ -3276,11 +3567,14 @@
       <c r="I63" s="1">
         <v>0</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="1">
+        <v>0</v>
+      </c>
+      <c r="K63" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>10062</v>
       </c>
@@ -3288,18 +3582,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Necklace_Tier3</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="1" t="str" cm="1">
+        <f t="array" ref="C64">_xlfn.IFS(F64&lt;=2, "Common", F64&lt;=4, "Uncommon", F64&lt;=6, "Rare", F64&lt;=8, "Epic", F64=9, "Legendary", F64&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E64" s="1">
+      <c r="F64" s="1">
         <v>3</v>
       </c>
-      <c r="F64" s="1">
-        <v>0</v>
-      </c>
       <c r="G64" s="1">
         <v>0</v>
       </c>
@@ -3309,11 +3604,14 @@
       <c r="I64" s="1">
         <v>0</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>10063</v>
       </c>
@@ -3321,18 +3619,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Necklace_Tier4</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="1" t="str" cm="1">
+        <f t="array" ref="C65">_xlfn.IFS(F65&lt;=2, "Common", F65&lt;=4, "Uncommon", F65&lt;=6, "Rare", F65&lt;=8, "Epic", F65=9, "Legendary", F65&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E65" s="1">
+      <c r="F65" s="1">
         <v>4</v>
       </c>
-      <c r="F65" s="1">
-        <v>0</v>
-      </c>
       <c r="G65" s="1">
         <v>0</v>
       </c>
@@ -3342,11 +3641,14 @@
       <c r="I65" s="1">
         <v>0</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>10064</v>
       </c>
@@ -3354,18 +3656,19 @@
         <f t="shared" si="0"/>
         <v>Equipment_Icon_Necklace_Tier5</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="1" t="str" cm="1">
+        <f t="array" ref="C66">_xlfn.IFS(F66&lt;=2, "Common", F66&lt;=4, "Uncommon", F66&lt;=6, "Rare", F66&lt;=8, "Epic", F66=9, "Legendary", F66&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E66" s="1">
+      <c r="F66" s="1">
         <v>5</v>
       </c>
-      <c r="F66" s="1">
-        <v>0</v>
-      </c>
       <c r="G66" s="1">
         <v>0</v>
       </c>
@@ -3375,30 +3678,34 @@
       <c r="I66" s="1">
         <v>0</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>10065</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f t="shared" ref="B67:B91" si="1">"Equipment_Icon_" &amp; D67 &amp; "_" &amp; "Tier" &amp; E67</f>
+        <f t="shared" ref="B67:B91" si="1">"Equipment_Icon_" &amp; E67 &amp; "_" &amp; "Tier" &amp; F67</f>
         <v>Equipment_Icon_Necklace_Tier6</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="1" t="str" cm="1">
+        <f t="array" ref="C67">_xlfn.IFS(F67&lt;=2, "Common", F67&lt;=4, "Uncommon", F67&lt;=6, "Rare", F67&lt;=8, "Epic", F67=9, "Legendary", F67&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E67" s="1">
+      <c r="F67" s="1">
         <v>6</v>
       </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
       <c r="G67" s="1">
         <v>0</v>
       </c>
@@ -3408,11 +3715,14 @@
       <c r="I67" s="1">
         <v>0</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>10066</v>
       </c>
@@ -3420,18 +3730,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Necklace_Tier7</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="1" t="str" cm="1">
+        <f t="array" ref="C68">_xlfn.IFS(F68&lt;=2, "Common", F68&lt;=4, "Uncommon", F68&lt;=6, "Rare", F68&lt;=8, "Epic", F68=9, "Legendary", F68&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E68" s="1">
+      <c r="F68" s="1">
         <v>7</v>
       </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
       <c r="G68" s="1">
         <v>0</v>
       </c>
@@ -3441,11 +3752,14 @@
       <c r="I68" s="1">
         <v>0</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>10067</v>
       </c>
@@ -3453,18 +3767,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Necklace_Tier8</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="1" t="str" cm="1">
+        <f t="array" ref="C69">_xlfn.IFS(F69&lt;=2, "Common", F69&lt;=4, "Uncommon", F69&lt;=6, "Rare", F69&lt;=8, "Epic", F69=9, "Legendary", F69&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E69" s="1">
+      <c r="F69" s="1">
         <v>8</v>
       </c>
-      <c r="F69" s="1">
-        <v>0</v>
-      </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
@@ -3474,11 +3789,14 @@
       <c r="I69" s="1">
         <v>0</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>10068</v>
       </c>
@@ -3486,18 +3804,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Necklace_Tier9</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="1" t="str" cm="1">
+        <f t="array" ref="C70">_xlfn.IFS(F70&lt;=2, "Common", F70&lt;=4, "Uncommon", F70&lt;=6, "Rare", F70&lt;=8, "Epic", F70=9, "Legendary", F70&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E70" s="1">
+      <c r="F70" s="1">
         <v>9</v>
       </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
@@ -3507,11 +3826,14 @@
       <c r="I70" s="1">
         <v>0</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>10069</v>
       </c>
@@ -3519,18 +3841,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Necklace_Tier10</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="1" t="str" cm="1">
+        <f t="array" ref="C71">_xlfn.IFS(F71&lt;=2, "Common", F71&lt;=4, "Uncommon", F71&lt;=6, "Rare", F71&lt;=8, "Epic", F71=9, "Legendary", F71&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E71" s="1">
+      <c r="F71" s="1">
         <v>10</v>
       </c>
-      <c r="F71" s="1">
-        <v>0</v>
-      </c>
       <c r="G71" s="1">
         <v>0</v>
       </c>
@@ -3540,11 +3863,14 @@
       <c r="I71" s="1">
         <v>0</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>10070</v>
       </c>
@@ -3552,18 +3878,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier1</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="1" t="str" cm="1">
+        <f t="array" ref="C72">_xlfn.IFS(F72&lt;=2, "Common", F72&lt;=4, "Uncommon", F72&lt;=6, "Rare", F72&lt;=8, "Epic", F72=9, "Legendary", F72&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E72" s="1">
+      <c r="F72" s="1">
         <v>1</v>
       </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
@@ -3573,11 +3900,14 @@
       <c r="I72" s="1">
         <v>0</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>10071</v>
       </c>
@@ -3585,18 +3915,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier2</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="1" t="str" cm="1">
+        <f t="array" ref="C73">_xlfn.IFS(F73&lt;=2, "Common", F73&lt;=4, "Uncommon", F73&lt;=6, "Rare", F73&lt;=8, "Epic", F73=9, "Legendary", F73&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E73" s="1">
+      <c r="F73" s="1">
         <v>2</v>
       </c>
-      <c r="F73" s="1">
-        <v>0</v>
-      </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
@@ -3606,11 +3937,14 @@
       <c r="I73" s="1">
         <v>0</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J73" s="1">
+        <v>0</v>
+      </c>
+      <c r="K73" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>10072</v>
       </c>
@@ -3618,18 +3952,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier3</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="1" t="str" cm="1">
+        <f t="array" ref="C74">_xlfn.IFS(F74&lt;=2, "Common", F74&lt;=4, "Uncommon", F74&lt;=6, "Rare", F74&lt;=8, "Epic", F74=9, "Legendary", F74&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E74" s="1">
+      <c r="F74" s="1">
         <v>3</v>
       </c>
-      <c r="F74" s="1">
-        <v>0</v>
-      </c>
       <c r="G74" s="1">
         <v>0</v>
       </c>
@@ -3639,11 +3974,14 @@
       <c r="I74" s="1">
         <v>0</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>10073</v>
       </c>
@@ -3651,18 +3989,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier4</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="1" t="str" cm="1">
+        <f t="array" ref="C75">_xlfn.IFS(F75&lt;=2, "Common", F75&lt;=4, "Uncommon", F75&lt;=6, "Rare", F75&lt;=8, "Epic", F75=9, "Legendary", F75&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E75" s="1">
+      <c r="F75" s="1">
         <v>4</v>
       </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
       <c r="G75" s="1">
         <v>0</v>
       </c>
@@ -3672,11 +4011,14 @@
       <c r="I75" s="1">
         <v>0</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>10074</v>
       </c>
@@ -3684,18 +4026,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier5</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="1" t="str" cm="1">
+        <f t="array" ref="C76">_xlfn.IFS(F76&lt;=2, "Common", F76&lt;=4, "Uncommon", F76&lt;=6, "Rare", F76&lt;=8, "Epic", F76=9, "Legendary", F76&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E76" s="1">
+      <c r="F76" s="1">
         <v>5</v>
       </c>
-      <c r="F76" s="1">
-        <v>0</v>
-      </c>
       <c r="G76" s="1">
         <v>0</v>
       </c>
@@ -3705,11 +4048,14 @@
       <c r="I76" s="1">
         <v>0</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>10075</v>
       </c>
@@ -3717,18 +4063,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier6</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="1" t="str" cm="1">
+        <f t="array" ref="C77">_xlfn.IFS(F77&lt;=2, "Common", F77&lt;=4, "Uncommon", F77&lt;=6, "Rare", F77&lt;=8, "Epic", F77=9, "Legendary", F77&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E77" s="1">
+      <c r="F77" s="1">
         <v>6</v>
       </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
       <c r="G77" s="1">
         <v>0</v>
       </c>
@@ -3738,11 +4085,14 @@
       <c r="I77" s="1">
         <v>0</v>
       </c>
-      <c r="J77" t="s">
+      <c r="J77" s="1">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>10076</v>
       </c>
@@ -3750,18 +4100,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier7</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="1" t="str" cm="1">
+        <f t="array" ref="C78">_xlfn.IFS(F78&lt;=2, "Common", F78&lt;=4, "Uncommon", F78&lt;=6, "Rare", F78&lt;=8, "Epic", F78=9, "Legendary", F78&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E78" s="1">
+      <c r="F78" s="1">
         <v>7</v>
       </c>
-      <c r="F78" s="1">
-        <v>0</v>
-      </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
@@ -3771,11 +4122,14 @@
       <c r="I78" s="1">
         <v>0</v>
       </c>
-      <c r="J78" t="s">
+      <c r="J78" s="1">
+        <v>0</v>
+      </c>
+      <c r="K78" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>10077</v>
       </c>
@@ -3783,18 +4137,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier8</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="1" t="str" cm="1">
+        <f t="array" ref="C79">_xlfn.IFS(F79&lt;=2, "Common", F79&lt;=4, "Uncommon", F79&lt;=6, "Rare", F79&lt;=8, "Epic", F79=9, "Legendary", F79&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E79" s="1">
+      <c r="F79" s="1">
         <v>8</v>
       </c>
-      <c r="F79" s="1">
-        <v>0</v>
-      </c>
       <c r="G79" s="1">
         <v>0</v>
       </c>
@@ -3804,11 +4159,14 @@
       <c r="I79" s="1">
         <v>0</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>10078</v>
       </c>
@@ -3816,18 +4174,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier9</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="1" t="str" cm="1">
+        <f t="array" ref="C80">_xlfn.IFS(F80&lt;=2, "Common", F80&lt;=4, "Uncommon", F80&lt;=6, "Rare", F80&lt;=8, "Epic", F80=9, "Legendary", F80&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E80" s="1">
+      <c r="F80" s="1">
         <v>9</v>
       </c>
-      <c r="F80" s="1">
-        <v>0</v>
-      </c>
       <c r="G80" s="1">
         <v>0</v>
       </c>
@@ -3837,11 +4196,14 @@
       <c r="I80" s="1">
         <v>0</v>
       </c>
-      <c r="J80" t="s">
+      <c r="J80" s="1">
+        <v>0</v>
+      </c>
+      <c r="K80" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>10079</v>
       </c>
@@ -3849,18 +4211,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Charm_Tier10</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="1" t="str" cm="1">
+        <f t="array" ref="C81">_xlfn.IFS(F81&lt;=2, "Common", F81&lt;=4, "Uncommon", F81&lt;=6, "Rare", F81&lt;=8, "Epic", F81=9, "Legendary", F81&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E81" s="1">
+      <c r="F81" s="1">
         <v>10</v>
       </c>
-      <c r="F81" s="1">
-        <v>0</v>
-      </c>
       <c r="G81" s="1">
         <v>0</v>
       </c>
@@ -3870,11 +4233,14 @@
       <c r="I81" s="1">
         <v>0</v>
       </c>
-      <c r="J81" t="s">
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>10080</v>
       </c>
@@ -3882,18 +4248,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier1</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="1" t="str" cm="1">
+        <f t="array" ref="C82">_xlfn.IFS(F82&lt;=2, "Common", F82&lt;=4, "Uncommon", F82&lt;=6, "Rare", F82&lt;=8, "Epic", F82=9, "Legendary", F82&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E82" s="1">
+      <c r="F82" s="1">
         <v>1</v>
       </c>
-      <c r="F82" s="1">
-        <v>0</v>
-      </c>
       <c r="G82" s="1">
         <v>0</v>
       </c>
@@ -3903,11 +4270,14 @@
       <c r="I82" s="1">
         <v>0</v>
       </c>
-      <c r="J82" t="s">
+      <c r="J82" s="1">
+        <v>0</v>
+      </c>
+      <c r="K82" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>10081</v>
       </c>
@@ -3915,18 +4285,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier2</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="1" t="str" cm="1">
+        <f t="array" ref="C83">_xlfn.IFS(F83&lt;=2, "Common", F83&lt;=4, "Uncommon", F83&lt;=6, "Rare", F83&lt;=8, "Epic", F83=9, "Legendary", F83&gt;=10, "Mythic")</f>
+        <v>Common</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E83" s="1">
+      <c r="F83" s="1">
         <v>2</v>
       </c>
-      <c r="F83" s="1">
-        <v>0</v>
-      </c>
       <c r="G83" s="1">
         <v>0</v>
       </c>
@@ -3936,11 +4307,14 @@
       <c r="I83" s="1">
         <v>0</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J83" s="1">
+        <v>0</v>
+      </c>
+      <c r="K83" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>10082</v>
       </c>
@@ -3948,18 +4322,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier3</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="1" t="str" cm="1">
+        <f t="array" ref="C84">_xlfn.IFS(F84&lt;=2, "Common", F84&lt;=4, "Uncommon", F84&lt;=6, "Rare", F84&lt;=8, "Epic", F84=9, "Legendary", F84&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E84" s="1">
+      <c r="F84" s="1">
         <v>3</v>
       </c>
-      <c r="F84" s="1">
-        <v>0</v>
-      </c>
       <c r="G84" s="1">
         <v>0</v>
       </c>
@@ -3969,11 +4344,14 @@
       <c r="I84" s="1">
         <v>0</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J84" s="1">
+        <v>0</v>
+      </c>
+      <c r="K84" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>10083</v>
       </c>
@@ -3981,18 +4359,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier4</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="1" t="str" cm="1">
+        <f t="array" ref="C85">_xlfn.IFS(F85&lt;=2, "Common", F85&lt;=4, "Uncommon", F85&lt;=6, "Rare", F85&lt;=8, "Epic", F85=9, "Legendary", F85&gt;=10, "Mythic")</f>
+        <v>Uncommon</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E85" s="1">
+      <c r="F85" s="1">
         <v>4</v>
       </c>
-      <c r="F85" s="1">
-        <v>0</v>
-      </c>
       <c r="G85" s="1">
         <v>0</v>
       </c>
@@ -4002,11 +4381,14 @@
       <c r="I85" s="1">
         <v>0</v>
       </c>
-      <c r="J85" t="s">
+      <c r="J85" s="1">
+        <v>0</v>
+      </c>
+      <c r="K85" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>10084</v>
       </c>
@@ -4014,18 +4396,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier5</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="1" t="str" cm="1">
+        <f t="array" ref="C86">_xlfn.IFS(F86&lt;=2, "Common", F86&lt;=4, "Uncommon", F86&lt;=6, "Rare", F86&lt;=8, "Epic", F86=9, "Legendary", F86&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E86" s="1">
+      <c r="F86" s="1">
         <v>5</v>
       </c>
-      <c r="F86" s="1">
-        <v>0</v>
-      </c>
       <c r="G86" s="1">
         <v>0</v>
       </c>
@@ -4035,11 +4418,14 @@
       <c r="I86" s="1">
         <v>0</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J86" s="1">
+        <v>0</v>
+      </c>
+      <c r="K86" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>10085</v>
       </c>
@@ -4047,18 +4433,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier6</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="1" t="str" cm="1">
+        <f t="array" ref="C87">_xlfn.IFS(F87&lt;=2, "Common", F87&lt;=4, "Uncommon", F87&lt;=6, "Rare", F87&lt;=8, "Epic", F87=9, "Legendary", F87&gt;=10, "Mythic")</f>
+        <v>Rare</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E87" s="1">
+      <c r="F87" s="1">
         <v>6</v>
       </c>
-      <c r="F87" s="1">
-        <v>0</v>
-      </c>
       <c r="G87" s="1">
         <v>0</v>
       </c>
@@ -4068,11 +4455,14 @@
       <c r="I87" s="1">
         <v>0</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J87" s="1">
+        <v>0</v>
+      </c>
+      <c r="K87" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>10086</v>
       </c>
@@ -4080,18 +4470,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier7</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="1" t="str" cm="1">
+        <f t="array" ref="C88">_xlfn.IFS(F88&lt;=2, "Common", F88&lt;=4, "Uncommon", F88&lt;=6, "Rare", F88&lt;=8, "Epic", F88=9, "Legendary", F88&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E88" s="1">
+      <c r="F88" s="1">
         <v>7</v>
       </c>
-      <c r="F88" s="1">
-        <v>0</v>
-      </c>
       <c r="G88" s="1">
         <v>0</v>
       </c>
@@ -4101,11 +4492,14 @@
       <c r="I88" s="1">
         <v>0</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J88" s="1">
+        <v>0</v>
+      </c>
+      <c r="K88" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>10087</v>
       </c>
@@ -4113,18 +4507,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier8</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="1" t="str" cm="1">
+        <f t="array" ref="C89">_xlfn.IFS(F89&lt;=2, "Common", F89&lt;=4, "Uncommon", F89&lt;=6, "Rare", F89&lt;=8, "Epic", F89=9, "Legendary", F89&gt;=10, "Mythic")</f>
+        <v>Epic</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E89" s="1">
+      <c r="F89" s="1">
         <v>8</v>
       </c>
-      <c r="F89" s="1">
-        <v>0</v>
-      </c>
       <c r="G89" s="1">
         <v>0</v>
       </c>
@@ -4134,11 +4529,14 @@
       <c r="I89" s="1">
         <v>0</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J89" s="1">
+        <v>0</v>
+      </c>
+      <c r="K89" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>10088</v>
       </c>
@@ -4146,18 +4544,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier9</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="1" t="str" cm="1">
+        <f t="array" ref="C90">_xlfn.IFS(F90&lt;=2, "Common", F90&lt;=4, "Uncommon", F90&lt;=6, "Rare", F90&lt;=8, "Epic", F90=9, "Legendary", F90&gt;=10, "Mythic")</f>
+        <v>Legendary</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E90" s="1">
+      <c r="F90" s="1">
         <v>9</v>
       </c>
-      <c r="F90" s="1">
-        <v>0</v>
-      </c>
       <c r="G90" s="1">
         <v>0</v>
       </c>
@@ -4167,11 +4566,14 @@
       <c r="I90" s="1">
         <v>0</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J90" s="1">
+        <v>0</v>
+      </c>
+      <c r="K90" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>10089</v>
       </c>
@@ -4179,18 +4581,19 @@
         <f t="shared" si="1"/>
         <v>Equipment_Icon_Watch_Tier10</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="1" t="str" cm="1">
+        <f t="array" ref="C91">_xlfn.IFS(F91&lt;=2, "Common", F91&lt;=4, "Uncommon", F91&lt;=6, "Rare", F91&lt;=8, "Epic", F91=9, "Legendary", F91&gt;=10, "Mythic")</f>
+        <v>Mythic</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E91" s="1">
+      <c r="F91" s="1">
         <v>10</v>
       </c>
-      <c r="F91" s="1">
-        <v>0</v>
-      </c>
       <c r="G91" s="1">
         <v>0</v>
       </c>
@@ -4200,30 +4603,34 @@
       <c r="I91" s="1">
         <v>0</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J91" s="1">
+        <v>0</v>
+      </c>
+      <c r="K91" t="s">
         <v>198</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1986D266-0A25-43B9-8C57-1B2DE3A951CA}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="14.375" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="6" width="10.25" customWidth="1"/>
-    <col min="7" max="7" width="35.625" customWidth="1"/>
-    <col min="8" max="8" width="18.875" customWidth="1"/>
+    <col min="2" max="4" width="14.375" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="10.25" customWidth="1"/>
+    <col min="8" max="8" width="35.625" customWidth="1"/>
+    <col min="9" max="9" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4231,22 +4638,25 @@
         <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>20000</v>
       </c>
@@ -4254,22 +4664,25 @@
         <v>211</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>50</v>
       </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
       <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
         <v>999</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4277,8 +4690,9 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4286,8 +4700,9 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -4295,8 +4710,9 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -4304,8 +4720,9 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4313,8 +4730,9 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -4322,8 +4740,9 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4331,8 +4750,9 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -4340,8 +4760,9 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4349,8 +4770,9 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4358,8 +4780,9 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4367,8 +4790,9 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4376,8 +4800,9 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4385,8 +4810,9 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4394,8 +4820,9 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4403,8 +4830,9 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4412,8 +4840,9 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4421,8 +4850,9 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -4430,8 +4860,9 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4439,6 +4870,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4448,16 +4880,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC68C5B-443D-45C4-801C-6E2A1C02F9D6}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.25" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
-    <col min="6" max="6" width="28.25" customWidth="1"/>
+    <col min="2" max="3" width="30.25" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11.875" customWidth="1"/>
+    <col min="7" max="7" width="28.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4465,21 +4897,24 @@
         <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>30000</v>
       </c>
@@ -4487,24 +4922,27 @@
         <v>202</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>9999</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>30001</v>
       </c>
@@ -4512,24 +4950,27 @@
         <v>205</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>9999</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>30002</v>
       </c>
@@ -4537,24 +4978,27 @@
         <v>206</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>9999</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -4566,8 +5010,9 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -4579,8 +5024,9 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4592,8 +5038,9 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -4605,8 +5052,9 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4618,8 +5066,9 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -4631,8 +5080,9 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4644,8 +5094,9 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4657,8 +5108,9 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4670,8 +5122,9 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4683,8 +5136,9 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4696,8 +5150,9 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4709,8 +5164,9 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4722,8 +5178,9 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4735,8 +5192,9 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4748,8 +5206,9 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -4761,8 +5220,9 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4774,8 +5234,9 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4787,8 +5248,9 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -4800,8 +5262,9 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -4813,8 +5276,9 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4826,8 +5290,9 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -4839,8 +5304,9 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4852,8 +5318,9 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4865,6 +5332,7 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/ExcelData/ItemTable.xlsx
+++ b/Assets/ExcelData/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1129889-43C1-40A5-9BF3-394CAAE9F820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748A246D-0ABF-4B99-974A-81F5CB08058B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -208,10 +208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Glove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EquipPart</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -845,6 +841,10 @@
   </si>
   <si>
     <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gloves</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier1</v>
+        <v>Equipment_Icon_Gloves_Tier1</v>
       </c>
       <c r="C12" s="1" t="str" cm="1">
         <f t="array" ref="C12">_xlfn.IFS(F12&lt;=2, "Common", F12&lt;=4, "Uncommon", F12&lt;=6, "Rare", F12&lt;=8, "Epic", F12=9, "Legendary", F12&gt;=10, "Mythic")</f>
@@ -1666,7 +1666,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier2</v>
+        <v>Equipment_Icon_Gloves_Tier2</v>
       </c>
       <c r="C13" s="1" t="str" cm="1">
         <f t="array" ref="C13">_xlfn.IFS(F13&lt;=2, "Common", F13&lt;=4, "Uncommon", F13&lt;=6, "Rare", F13&lt;=8, "Epic", F13=9, "Legendary", F13&gt;=10, "Mythic")</f>
@@ -1703,7 +1703,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F13" s="1">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier3</v>
+        <v>Equipment_Icon_Gloves_Tier3</v>
       </c>
       <c r="C14" s="1" t="str" cm="1">
         <f t="array" ref="C14">_xlfn.IFS(F14&lt;=2, "Common", F14&lt;=4, "Uncommon", F14&lt;=6, "Rare", F14&lt;=8, "Epic", F14=9, "Legendary", F14&gt;=10, "Mythic")</f>
@@ -1740,7 +1740,7 @@
         <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="B15" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier4</v>
+        <v>Equipment_Icon_Gloves_Tier4</v>
       </c>
       <c r="C15" s="1" t="str" cm="1">
         <f t="array" ref="C15">_xlfn.IFS(F15&lt;=2, "Common", F15&lt;=4, "Uncommon", F15&lt;=6, "Rare", F15&lt;=8, "Epic", F15=9, "Legendary", F15&gt;=10, "Mythic")</f>
@@ -1777,7 +1777,7 @@
         <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier5</v>
+        <v>Equipment_Icon_Gloves_Tier5</v>
       </c>
       <c r="C16" s="1" t="str" cm="1">
         <f t="array" ref="C16">_xlfn.IFS(F16&lt;=2, "Common", F16&lt;=4, "Uncommon", F16&lt;=6, "Rare", F16&lt;=8, "Epic", F16=9, "Legendary", F16&gt;=10, "Mythic")</f>
@@ -1814,7 +1814,7 @@
         <v>33</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F16" s="1">
         <v>5</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier6</v>
+        <v>Equipment_Icon_Gloves_Tier6</v>
       </c>
       <c r="C17" s="1" t="str" cm="1">
         <f t="array" ref="C17">_xlfn.IFS(F17&lt;=2, "Common", F17&lt;=4, "Uncommon", F17&lt;=6, "Rare", F17&lt;=8, "Epic", F17=9, "Legendary", F17&gt;=10, "Mythic")</f>
@@ -1851,7 +1851,7 @@
         <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F17" s="1">
         <v>6</v>
@@ -1869,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier7</v>
+        <v>Equipment_Icon_Gloves_Tier7</v>
       </c>
       <c r="C18" s="1" t="str" cm="1">
         <f t="array" ref="C18">_xlfn.IFS(F18&lt;=2, "Common", F18&lt;=4, "Uncommon", F18&lt;=6, "Rare", F18&lt;=8, "Epic", F18=9, "Legendary", F18&gt;=10, "Mythic")</f>
@@ -1888,7 +1888,7 @@
         <v>35</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F18" s="1">
         <v>7</v>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="B19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier8</v>
+        <v>Equipment_Icon_Gloves_Tier8</v>
       </c>
       <c r="C19" s="1" t="str" cm="1">
         <f t="array" ref="C19">_xlfn.IFS(F19&lt;=2, "Common", F19&lt;=4, "Uncommon", F19&lt;=6, "Rare", F19&lt;=8, "Epic", F19=9, "Legendary", F19&gt;=10, "Mythic")</f>
@@ -1925,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F19" s="1">
         <v>8</v>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier9</v>
+        <v>Equipment_Icon_Gloves_Tier9</v>
       </c>
       <c r="C20" s="1" t="str" cm="1">
         <f t="array" ref="C20">_xlfn.IFS(F20&lt;=2, "Common", F20&lt;=4, "Uncommon", F20&lt;=6, "Rare", F20&lt;=8, "Epic", F20=9, "Legendary", F20&gt;=10, "Mythic")</f>
@@ -1962,7 +1962,7 @@
         <v>37</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F20" s="1">
         <v>9</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B21" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Equipment_Icon_Glove_Tier10</v>
+        <v>Equipment_Icon_Gloves_Tier10</v>
       </c>
       <c r="C21" s="1" t="str" cm="1">
         <f t="array" ref="C21">_xlfn.IFS(F21&lt;=2, "Common", F21&lt;=4, "Uncommon", F21&lt;=6, "Rare", F21&lt;=8, "Epic", F21=9, "Legendary", F21&gt;=10, "Mythic")</f>
@@ -1999,7 +1999,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="F21" s="1">
         <v>10</v>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -2033,10 +2033,10 @@
         <v>Common</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -2070,10 +2070,10 @@
         <v>Common</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" s="1">
         <v>2</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -2107,10 +2107,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -2144,10 +2144,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F25" s="1">
         <v>4</v>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -2181,10 +2181,10 @@
         <v>Rare</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F26" s="1">
         <v>5</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -2218,10 +2218,10 @@
         <v>Rare</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F27" s="1">
         <v>6</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -2255,10 +2255,10 @@
         <v>Epic</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F28" s="1">
         <v>7</v>
@@ -2276,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
@@ -2292,10 +2292,10 @@
         <v>Epic</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F29" s="1">
         <v>8</v>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -2329,10 +2329,10 @@
         <v>Legendary</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F30" s="1">
         <v>9</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -2366,10 +2366,10 @@
         <v>Mythic</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F31" s="1">
         <v>10</v>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -2403,10 +2403,10 @@
         <v>Common</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -2440,10 +2440,10 @@
         <v>Common</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F33" s="1">
         <v>2</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -2477,10 +2477,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F34" s="1">
         <v>3</v>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -2514,10 +2514,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35" s="1">
         <v>4</v>
@@ -2535,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
@@ -2551,10 +2551,10 @@
         <v>Rare</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F36" s="1">
         <v>5</v>
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -2588,10 +2588,10 @@
         <v>Rare</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F37" s="1">
         <v>6</v>
@@ -2609,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -2625,10 +2625,10 @@
         <v>Epic</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F38" s="1">
         <v>7</v>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -2662,10 +2662,10 @@
         <v>Epic</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F39" s="1">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
@@ -2699,10 +2699,10 @@
         <v>Legendary</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F40" s="1">
         <v>9</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
@@ -2736,10 +2736,10 @@
         <v>Mythic</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F41" s="1">
         <v>10</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -2773,10 +2773,10 @@
         <v>Common</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
@@ -2810,10 +2810,10 @@
         <v>Common</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F43" s="1">
         <v>2</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
@@ -2847,10 +2847,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F44" s="1">
         <v>3</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
@@ -2884,10 +2884,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F45" s="1">
         <v>4</v>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
@@ -2921,10 +2921,10 @@
         <v>Rare</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F46" s="1">
         <v>5</v>
@@ -2942,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
@@ -2958,10 +2958,10 @@
         <v>Rare</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F47" s="1">
         <v>6</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
@@ -2995,10 +2995,10 @@
         <v>Epic</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F48" s="1">
         <v>7</v>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
@@ -3032,10 +3032,10 @@
         <v>Epic</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F49" s="1">
         <v>8</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
@@ -3069,10 +3069,10 @@
         <v>Legendary</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F50" s="1">
         <v>9</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
@@ -3106,10 +3106,10 @@
         <v>Mythic</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F51" s="1">
         <v>10</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
@@ -3143,10 +3143,10 @@
         <v>Common</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F52" s="1">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
@@ -3180,10 +3180,10 @@
         <v>Common</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F53" s="1">
         <v>2</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
@@ -3217,10 +3217,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F54" s="1">
         <v>3</v>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
@@ -3254,10 +3254,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F55" s="1">
         <v>4</v>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -3291,10 +3291,10 @@
         <v>Rare</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F56" s="1">
         <v>5</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
@@ -3328,10 +3328,10 @@
         <v>Rare</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F57" s="1">
         <v>6</v>
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
@@ -3365,10 +3365,10 @@
         <v>Epic</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F58" s="1">
         <v>7</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
@@ -3402,10 +3402,10 @@
         <v>Epic</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F59" s="1">
         <v>8</v>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
@@ -3439,10 +3439,10 @@
         <v>Legendary</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F60" s="1">
         <v>9</v>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
@@ -3476,10 +3476,10 @@
         <v>Mythic</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F61" s="1">
         <v>10</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
@@ -3513,10 +3513,10 @@
         <v>Common</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F62" s="1">
         <v>1</v>
@@ -3534,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
@@ -3550,10 +3550,10 @@
         <v>Common</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -3571,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
@@ -3587,10 +3587,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F64" s="1">
         <v>3</v>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
@@ -3624,10 +3624,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F65" s="1">
         <v>4</v>
@@ -3645,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
@@ -3661,10 +3661,10 @@
         <v>Rare</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F66" s="1">
         <v>5</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
@@ -3698,10 +3698,10 @@
         <v>Rare</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F67" s="1">
         <v>6</v>
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
@@ -3735,10 +3735,10 @@
         <v>Epic</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F68" s="1">
         <v>7</v>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
@@ -3772,10 +3772,10 @@
         <v>Epic</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F69" s="1">
         <v>8</v>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
@@ -3809,10 +3809,10 @@
         <v>Legendary</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F70" s="1">
         <v>9</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
@@ -3846,10 +3846,10 @@
         <v>Mythic</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F71" s="1">
         <v>10</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
@@ -3883,10 +3883,10 @@
         <v>Common</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
@@ -3920,10 +3920,10 @@
         <v>Common</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F73" s="1">
         <v>2</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
@@ -3957,10 +3957,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F74" s="1">
         <v>3</v>
@@ -3978,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
@@ -3994,10 +3994,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F75" s="1">
         <v>4</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
@@ -4031,10 +4031,10 @@
         <v>Rare</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F76" s="1">
         <v>5</v>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
@@ -4068,10 +4068,10 @@
         <v>Rare</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F77" s="1">
         <v>6</v>
@@ -4089,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
@@ -4105,10 +4105,10 @@
         <v>Epic</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F78" s="1">
         <v>7</v>
@@ -4126,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
@@ -4142,10 +4142,10 @@
         <v>Epic</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F79" s="1">
         <v>8</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
@@ -4179,10 +4179,10 @@
         <v>Legendary</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F80" s="1">
         <v>9</v>
@@ -4200,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
@@ -4216,10 +4216,10 @@
         <v>Mythic</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F81" s="1">
         <v>10</v>
@@ -4237,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
@@ -4253,10 +4253,10 @@
         <v>Common</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F82" s="1">
         <v>1</v>
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
@@ -4290,10 +4290,10 @@
         <v>Common</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F83" s="1">
         <v>2</v>
@@ -4311,7 +4311,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
@@ -4327,10 +4327,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F84" s="1">
         <v>3</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
@@ -4364,10 +4364,10 @@
         <v>Uncommon</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F85" s="1">
         <v>4</v>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
@@ -4401,10 +4401,10 @@
         <v>Rare</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F86" s="1">
         <v>5</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
@@ -4438,10 +4438,10 @@
         <v>Rare</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F87" s="1">
         <v>6</v>
@@ -4459,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
@@ -4475,10 +4475,10 @@
         <v>Epic</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F88" s="1">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
@@ -4512,10 +4512,10 @@
         <v>Epic</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F89" s="1">
         <v>8</v>
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
@@ -4549,10 +4549,10 @@
         <v>Legendary</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F90" s="1">
         <v>9</v>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
@@ -4586,10 +4586,10 @@
         <v>Mythic</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F91" s="1">
         <v>10</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4635,22 +4635,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -4661,13 +4661,13 @@
         <v>20000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -4679,7 +4679,7 @@
         <v>999</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4894,10 +4894,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -4906,7 +4906,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -4919,13 +4919,13 @@
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -4934,7 +4934,7 @@
         <v>9999</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -4947,13 +4947,13 @@
         <v>30001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -4962,7 +4962,7 @@
         <v>9999</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -4975,13 +4975,13 @@
         <v>30002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E4" s="1">
         <v>3</v>
@@ -4990,7 +4990,7 @@
         <v>9999</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>

--- a/Assets/ExcelData/ItemTable.xlsx
+++ b/Assets/ExcelData/ItemTable.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8F7A67-03A3-4428-88FA-A3EDCD50F611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F87CFB7-732E-4853-B9CD-B667799D8E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="855" windowWidth="21600" windowHeight="11385" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="714" firstSheet="1" activeTab="4" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
     <sheet name="StatPool" sheetId="4" r:id="rId2"/>
     <sheet name="Consumable" sheetId="2" r:id="rId3"/>
     <sheet name="Material" sheetId="3" r:id="rId4"/>
-    <sheet name="EquipPartMapping" sheetId="5" r:id="rId5"/>
-    <sheet name="TierMapping" sheetId="6" r:id="rId6"/>
+    <sheet name="EquipmentLevelExpData" sheetId="7" r:id="rId5"/>
+    <sheet name="EquipmentDecomposition" sheetId="8" r:id="rId6"/>
+    <sheet name="EquipPartMapping" sheetId="5" r:id="rId7"/>
+    <sheet name="TierMapping" sheetId="6" r:id="rId8"/>
+    <sheet name="EquipmentUpgradeBookExp" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="325">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1116,6 +1119,74 @@
   </si>
   <si>
     <t>[Tier10 SubStat]</t>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequireExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_EquipmentUpgradeBook_Tier1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_EquipmentUpgradeBook_Tier3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_EquipmentUpgradeBook_Tier2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전술 장비 강화 재료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mat1_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mat1_Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mat3_Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mat3_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mat2_Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mat2_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">소형 전술 매뉴얼	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">중형 전술 매뉴얼	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">대형 전술 매뉴얼	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mat_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -9702,8 +9773,9 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="30.25" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="2" max="2" width="33.5" customWidth="1"/>
+    <col min="3" max="3" width="30.25" customWidth="1"/>
+    <col min="4" max="4" width="23.625" customWidth="1"/>
     <col min="6" max="6" width="11.875" customWidth="1"/>
     <col min="7" max="7" width="28.25" customWidth="1"/>
   </cols>
@@ -9818,13 +9890,27 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="A5" s="1">
+        <v>30003</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>9999</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -9832,13 +9918,27 @@
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="A6" s="1">
+        <v>30004</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>9999</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -9846,13 +9946,27 @@
       <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="A7" s="1">
+        <v>30005</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>9999</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -10160,6 +10274,485 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11031213-A96E-48AE-9979-BF10E514BD27}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.75" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>6150</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE16E58-B954-4DC3-AA95-8384A11267D9}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C2" s="1">
+        <f>ROUND(2*A2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E2" s="1">
+        <f>MAX(0,ROUND(A2-2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G2" s="1">
+        <f>MAX(0,ROUND((A2-5)/2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" ref="C3:C11" si="0">ROUND(2*A3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="D3" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:E11" si="1">MAX(0,ROUND(A3-2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" ref="G3:G11" si="2">MAX(0,ROUND((A3-5)/2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D4" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D6" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="D7" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F7" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="D9" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F9" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="D10" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="F10" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
+        <v>30004</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="F11" s="1">
+        <v>30005</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AEF480A-6299-43DA-A60A-6003AF21D987}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10290,7 +10883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAEF290D-EF41-4D42-8CEE-0743F32935E5}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10424,4 +11017,51 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD1EFD9-F8F2-4764-9470-45DFB13D7E05}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>30003</v>
+      </c>
+      <c r="B2" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>30004</v>
+      </c>
+      <c r="B3" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>30005</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/ExcelData/ItemTable.xlsx
+++ b/Assets/ExcelData/ItemTable.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1CA696-5111-450E-BC28-7F9A01304FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31005" yWindow="1530" windowWidth="21600" windowHeight="11385" tabRatio="791" activeTab="3" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
+    <workbookView xWindow="8355" yWindow="2685" windowWidth="21600" windowHeight="11385" tabRatio="791" activeTab="7" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -1267,12 +1267,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5258,10 +5255,10 @@
       <c r="D1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>334</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -5281,10 +5278,10 @@
       <c r="D2" s="1">
         <v>100</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>25</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -5304,10 +5301,10 @@
       <c r="D3" s="1">
         <v>10</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>3</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>3</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -5327,10 +5324,10 @@
       <c r="D4" s="1">
         <v>0.05</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>0.01</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>0.01</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -5350,10 +5347,10 @@
       <c r="D5" s="1">
         <v>0.05</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>0.01</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>0.01</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -5373,10 +5370,10 @@
       <c r="D6" s="1">
         <v>0.06</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -5396,10 +5393,10 @@
       <c r="D7" s="1">
         <v>0.03</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -5419,10 +5416,10 @@
       <c r="D8" s="1">
         <v>0.05</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -5442,10 +5439,10 @@
       <c r="D9" s="1">
         <v>0.05</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>0.01</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>0.01</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -5465,10 +5462,10 @@
       <c r="D10" s="1">
         <v>0.05</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>0.01</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>0.01</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -5488,10 +5485,10 @@
       <c r="D11" s="1">
         <v>0.06</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -5511,10 +5508,10 @@
       <c r="D12" s="1">
         <v>0.03</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -5534,10 +5531,10 @@
       <c r="D13" s="1">
         <v>0.05</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -5557,10 +5554,10 @@
       <c r="D14" s="1">
         <v>0.06</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -5580,10 +5577,10 @@
       <c r="D15" s="1">
         <v>50</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>9.5</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>14.5</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -5603,10 +5600,10 @@
       <c r="D16" s="1">
         <v>5</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -5626,10 +5623,10 @@
       <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -5649,10 +5646,10 @@
       <c r="D18" s="1">
         <v>0.03</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -5672,10 +5669,10 @@
       <c r="D19" s="1">
         <v>0.03</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="1">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -5695,10 +5692,10 @@
       <c r="D20" s="1">
         <v>0.04</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -5718,10 +5715,10 @@
       <c r="D21" s="1">
         <v>0.01</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="1">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -5741,10 +5738,10 @@
       <c r="D22" s="1">
         <v>0.04</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -5764,10 +5761,10 @@
       <c r="D23" s="1">
         <v>0.02</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -5787,10 +5784,10 @@
       <c r="D24" s="1">
         <v>0.04</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -5810,10 +5807,10 @@
       <c r="D25" s="1">
         <v>130</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>32.5</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>32.5</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -5833,10 +5830,10 @@
       <c r="D26" s="1">
         <v>13</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="1">
         <v>3.9</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>3.9</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -5856,10 +5853,10 @@
       <c r="D27" s="1">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -5879,10 +5876,10 @@
       <c r="D28" s="1">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -5902,10 +5899,10 @@
       <c r="D29" s="1">
         <v>7.8E-2</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -5925,10 +5922,10 @@
       <c r="D30" s="1">
         <v>3.9E-2</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="1">
         <v>1.04E-2</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="1">
         <v>1.04E-2</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -5948,10 +5945,10 @@
       <c r="D31" s="1">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -5971,10 +5968,10 @@
       <c r="D32" s="1">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -5994,10 +5991,10 @@
       <c r="D33" s="1">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -6017,10 +6014,10 @@
       <c r="D34" s="1">
         <v>7.8E-2</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -6040,10 +6037,10 @@
       <c r="D35" s="1">
         <v>3.9E-2</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="1">
         <v>1.04E-2</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>1.04E-2</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -6063,10 +6060,10 @@
       <c r="D36" s="1">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -6086,10 +6083,10 @@
       <c r="D37" s="1">
         <v>7.8E-2</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -6109,10 +6106,10 @@
       <c r="D38" s="1">
         <v>65</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>12.5</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="1">
         <v>18.5</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -6132,10 +6129,10 @@
       <c r="D39" s="1">
         <v>6.5</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>1.5</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>2.5</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -6155,10 +6152,10 @@
       <c r="D40" s="1">
         <v>6.5</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="1">
         <v>1.5</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>2.5</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -6178,10 +6175,10 @@
       <c r="D41" s="1">
         <v>3.9E-2</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="1">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="1">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -6201,10 +6198,10 @@
       <c r="D42" s="1">
         <v>3.9E-2</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="1">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -6224,10 +6221,10 @@
       <c r="D43" s="1">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="1">
         <v>1.04E-2</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -6247,10 +6244,10 @@
       <c r="D44" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="1">
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -6270,10 +6267,10 @@
       <c r="D45" s="1">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="1">
         <v>1.04E-2</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -6293,10 +6290,10 @@
       <c r="D46" s="1">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="1">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="1">
         <v>7.7999999999999996E-3</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -6316,10 +6313,10 @@
       <c r="D47" s="1">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="1">
         <v>1.04E-2</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="1">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -6339,10 +6336,10 @@
       <c r="D48" s="1">
         <v>160</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="1">
         <v>40</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>40</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -6362,10 +6359,10 @@
       <c r="D49" s="1">
         <v>16</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>4.8</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>4.8</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -6385,10 +6382,10 @@
       <c r="D50" s="1">
         <v>0.08</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>1.6E-2</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -6408,10 +6405,10 @@
       <c r="D51" s="1">
         <v>0.08</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="1">
         <v>1.6E-2</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -6431,10 +6428,10 @@
       <c r="D52" s="1">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -6454,10 +6451,10 @@
       <c r="D53" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -6477,10 +6474,10 @@
       <c r="D54" s="1">
         <v>0.08</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -6500,10 +6497,10 @@
       <c r="D55" s="1">
         <v>0.08</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="1">
         <v>1.6E-2</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -6523,10 +6520,10 @@
       <c r="D56" s="1">
         <v>0.08</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="1">
         <v>1.6E-2</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -6546,10 +6543,10 @@
       <c r="D57" s="1">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -6569,10 +6566,10 @@
       <c r="D58" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -6592,10 +6589,10 @@
       <c r="D59" s="1">
         <v>0.08</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G59" s="1" t="s">
@@ -6615,10 +6612,10 @@
       <c r="D60" s="1">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G60" s="1" t="s">
@@ -6638,10 +6635,10 @@
       <c r="D61" s="1">
         <v>80</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="1">
         <v>15.5</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="1">
         <v>23</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -6661,10 +6658,10 @@
       <c r="D62" s="1">
         <v>8</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>2</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="1">
         <v>3</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -6684,10 +6681,10 @@
       <c r="D63" s="1">
         <v>8</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="1">
         <v>3</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -6707,10 +6704,10 @@
       <c r="D64" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="1">
         <v>1.54E-2</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -6730,10 +6727,10 @@
       <c r="D65" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="1">
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="1">
         <v>1.54E-2</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -6753,10 +6750,10 @@
       <c r="D66" s="1">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -6776,10 +6773,10 @@
       <c r="D67" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>3.8E-3</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="1">
         <v>5.7999999999999996E-3</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -6799,10 +6796,10 @@
       <c r="D68" s="1">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G68" s="1" t="s">
@@ -6822,10 +6819,10 @@
       <c r="D69" s="1">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="1">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="G69" s="1" t="s">
@@ -6845,10 +6842,10 @@
       <c r="D70" s="1">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G70" s="1" t="s">
@@ -6868,10 +6865,10 @@
       <c r="D71" s="1">
         <v>200</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>50</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="1">
         <v>50</v>
       </c>
       <c r="G71" s="1" t="s">
@@ -6891,10 +6888,10 @@
       <c r="D72" s="1">
         <v>20</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="1">
         <v>6</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="1">
         <v>6</v>
       </c>
       <c r="G72" s="1" t="s">
@@ -6914,10 +6911,10 @@
       <c r="D73" s="1">
         <v>0.1</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>0.02</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="1">
         <v>0.02</v>
       </c>
       <c r="G73" s="1" t="s">
@@ -6937,10 +6934,10 @@
       <c r="D74" s="1">
         <v>0.1</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="1">
         <v>0.02</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="1">
         <v>0.02</v>
       </c>
       <c r="G74" s="1" t="s">
@@ -6960,10 +6957,10 @@
       <c r="D75" s="1">
         <v>0.12</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G75" s="1" t="s">
@@ -6983,10 +6980,10 @@
       <c r="D76" s="1">
         <v>0.06</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>1.6E-2</v>
       </c>
       <c r="G76" s="1" t="s">
@@ -7006,10 +7003,10 @@
       <c r="D77" s="1">
         <v>0.1</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G77" s="1" t="s">
@@ -7029,10 +7026,10 @@
       <c r="D78" s="1">
         <v>0.1</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>0.02</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="1">
         <v>0.02</v>
       </c>
       <c r="G78" s="1" t="s">
@@ -7052,10 +7049,10 @@
       <c r="D79" s="1">
         <v>0.1</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="1">
         <v>0.02</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="1">
         <v>0.02</v>
       </c>
       <c r="G79" s="1" t="s">
@@ -7075,10 +7072,10 @@
       <c r="D80" s="1">
         <v>0.12</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G80" s="1" t="s">
@@ -7098,10 +7095,10 @@
       <c r="D81" s="1">
         <v>0.06</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="1">
         <v>1.6E-2</v>
       </c>
       <c r="G81" s="1" t="s">
@@ -7121,10 +7118,10 @@
       <c r="D82" s="1">
         <v>0.1</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G82" s="1" t="s">
@@ -7144,10 +7141,10 @@
       <c r="D83" s="1">
         <v>0.12</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G83" s="1" t="s">
@@ -7167,10 +7164,10 @@
       <c r="D84" s="1">
         <v>100</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="1">
         <v>19</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="1">
         <v>29</v>
       </c>
       <c r="G84" s="1" t="s">
@@ -7190,10 +7187,10 @@
       <c r="D85" s="1">
         <v>10</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>2.5</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="1">
         <v>3.5</v>
       </c>
       <c r="G85" s="1" t="s">
@@ -7213,10 +7210,10 @@
       <c r="D86" s="1">
         <v>10</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="1">
         <v>2.5</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="1">
         <v>3.5</v>
       </c>
       <c r="G86" s="1" t="s">
@@ -7236,10 +7233,10 @@
       <c r="D87" s="1">
         <v>0.06</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G87" s="1" t="s">
@@ -7259,10 +7256,10 @@
       <c r="D88" s="1">
         <v>0.06</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="1">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
       <c r="G88" s="1" t="s">
@@ -7282,10 +7279,10 @@
       <c r="D89" s="1">
         <v>0.08</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G89" s="1" t="s">
@@ -7305,10 +7302,10 @@
       <c r="D90" s="1">
         <v>0.02</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="1">
         <v>7.1999999999999998E-3</v>
       </c>
       <c r="G90" s="1" t="s">
@@ -7328,10 +7325,10 @@
       <c r="D91" s="1">
         <v>0.08</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G91" s="1" t="s">
@@ -7351,10 +7348,10 @@
       <c r="D92" s="1">
         <v>0.04</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="1">
         <v>1.2E-2</v>
       </c>
       <c r="G92" s="1" t="s">
@@ -7374,10 +7371,10 @@
       <c r="D93" s="1">
         <v>0.08</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G93" s="1" t="s">
@@ -7397,10 +7394,10 @@
       <c r="D94" s="1">
         <v>250</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="1">
         <v>62.5</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="1">
         <v>62.5</v>
       </c>
       <c r="G94" s="1" t="s">
@@ -7420,10 +7417,10 @@
       <c r="D95" s="1">
         <v>25</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95" s="1">
         <v>7.5</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="1">
         <v>7.5</v>
       </c>
       <c r="G95" s="1" t="s">
@@ -7443,10 +7440,10 @@
       <c r="D96" s="1">
         <v>0.125</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G96" s="1" t="s">
@@ -7466,10 +7463,10 @@
       <c r="D97" s="1">
         <v>0.125</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G97" s="1" t="s">
@@ -7489,10 +7486,10 @@
       <c r="D98" s="1">
         <v>0.15</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E98" s="1">
         <v>0.03</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="1">
         <v>0.03</v>
       </c>
       <c r="G98" s="1" t="s">
@@ -7512,10 +7509,10 @@
       <c r="D99" s="1">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>0.02</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="1">
         <v>0.02</v>
       </c>
       <c r="G99" s="1" t="s">
@@ -7535,10 +7532,10 @@
       <c r="D100" s="1">
         <v>0.125</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>0.03</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="1">
         <v>0.03</v>
       </c>
       <c r="G100" s="1" t="s">
@@ -7558,10 +7555,10 @@
       <c r="D101" s="1">
         <v>0.125</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E101" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G101" s="1" t="s">
@@ -7581,10 +7578,10 @@
       <c r="D102" s="1">
         <v>0.125</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G102" s="1" t="s">
@@ -7604,10 +7601,10 @@
       <c r="D103" s="1">
         <v>0.15</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>0.03</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="1">
         <v>0.03</v>
       </c>
       <c r="G103" s="1" t="s">
@@ -7627,10 +7624,10 @@
       <c r="D104" s="1">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E104" s="1">
         <v>0.02</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="1">
         <v>0.02</v>
       </c>
       <c r="G104" s="1" t="s">
@@ -7650,10 +7647,10 @@
       <c r="D105" s="1">
         <v>0.125</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E105" s="1">
         <v>0.03</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="1">
         <v>0.03</v>
       </c>
       <c r="G105" s="1" t="s">
@@ -7673,10 +7670,10 @@
       <c r="D106" s="1">
         <v>0.15</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="1">
         <v>0.03</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="1">
         <v>0.03</v>
       </c>
       <c r="G106" s="1" t="s">
@@ -7696,10 +7693,10 @@
       <c r="D107" s="1">
         <v>125</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>24</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="1">
         <v>36</v>
       </c>
       <c r="G107" s="1" t="s">
@@ -7719,10 +7716,10 @@
       <c r="D108" s="1">
         <v>12.5</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E108" s="1">
         <v>3</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="1">
         <v>4.5</v>
       </c>
       <c r="G108" s="1" t="s">
@@ -7742,10 +7739,10 @@
       <c r="D109" s="1">
         <v>12.5</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="1">
         <v>3</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="1">
         <v>4.5</v>
       </c>
       <c r="G109" s="1" t="s">
@@ -7765,10 +7762,10 @@
       <c r="D110" s="1">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E110" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G110" s="1" t="s">
@@ -7788,10 +7785,10 @@
       <c r="D111" s="1">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G111" s="1" t="s">
@@ -7811,10 +7808,10 @@
       <c r="D112" s="1">
         <v>0.1</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="1">
         <v>0.02</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="1">
         <v>0.03</v>
       </c>
       <c r="G112" s="1" t="s">
@@ -7834,10 +7831,10 @@
       <c r="D113" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E113" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="G113" s="1" t="s">
@@ -7857,10 +7854,10 @@
       <c r="D114" s="1">
         <v>0.1</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>0.02</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="1">
         <v>0.03</v>
       </c>
       <c r="G114" s="1" t="s">
@@ -7880,10 +7877,10 @@
       <c r="D115" s="1">
         <v>0.05</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E115" s="1">
         <v>0.01</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G115" s="1" t="s">
@@ -7903,10 +7900,10 @@
       <c r="D116" s="1">
         <v>0.1</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E116" s="1">
         <v>0.02</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="1">
         <v>0.03</v>
       </c>
       <c r="G116" s="1" t="s">
@@ -7926,10 +7923,10 @@
       <c r="D117" s="1">
         <v>300</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="1">
         <v>75</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="1">
         <v>75</v>
       </c>
       <c r="G117" s="1" t="s">
@@ -7949,10 +7946,10 @@
       <c r="D118" s="1">
         <v>30</v>
       </c>
-      <c r="E118" s="2">
+      <c r="E118" s="1">
         <v>9</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="1">
         <v>9</v>
       </c>
       <c r="G118" s="1" t="s">
@@ -7972,10 +7969,10 @@
       <c r="D119" s="1">
         <v>0.15</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>0.03</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="1">
         <v>0.03</v>
       </c>
       <c r="G119" s="1" t="s">
@@ -7995,10 +7992,10 @@
       <c r="D120" s="1">
         <v>0.15</v>
       </c>
-      <c r="E120" s="2">
+      <c r="E120" s="1">
         <v>0.03</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="1">
         <v>0.03</v>
       </c>
       <c r="G120" s="1" t="s">
@@ -8018,10 +8015,10 @@
       <c r="D121" s="1">
         <v>0.18</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E121" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G121" s="1" t="s">
@@ -8041,10 +8038,10 @@
       <c r="D122" s="1">
         <v>0.09</v>
       </c>
-      <c r="E122" s="2">
+      <c r="E122" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G122" s="1" t="s">
@@ -8064,10 +8061,10 @@
       <c r="D123" s="1">
         <v>0.15</v>
       </c>
-      <c r="E123" s="2">
+      <c r="E123" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G123" s="1" t="s">
@@ -8087,10 +8084,10 @@
       <c r="D124" s="1">
         <v>0.15</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="1">
         <v>0.03</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="1">
         <v>0.03</v>
       </c>
       <c r="G124" s="1" t="s">
@@ -8110,10 +8107,10 @@
       <c r="D125" s="1">
         <v>0.15</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>0.03</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="1">
         <v>0.03</v>
       </c>
       <c r="G125" s="1" t="s">
@@ -8133,10 +8130,10 @@
       <c r="D126" s="1">
         <v>0.18</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G126" s="1" t="s">
@@ -8156,10 +8153,10 @@
       <c r="D127" s="1">
         <v>0.09</v>
       </c>
-      <c r="E127" s="2">
+      <c r="E127" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="1">
         <v>2.4E-2</v>
       </c>
       <c r="G127" s="1" t="s">
@@ -8179,10 +8176,10 @@
       <c r="D128" s="1">
         <v>0.15</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G128" s="1" t="s">
@@ -8202,10 +8199,10 @@
       <c r="D129" s="1">
         <v>0.18</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G129" s="1" t="s">
@@ -8225,10 +8222,10 @@
       <c r="D130" s="1">
         <v>150</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E130" s="1">
         <v>29</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="1">
         <v>43</v>
       </c>
       <c r="G130" s="1" t="s">
@@ -8248,10 +8245,10 @@
       <c r="D131" s="1">
         <v>15</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>3.5</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="1">
         <v>5.5</v>
       </c>
       <c r="G131" s="1" t="s">
@@ -8271,10 +8268,10 @@
       <c r="D132" s="1">
         <v>15</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>3.5</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="1">
         <v>5.5</v>
       </c>
       <c r="G132" s="1" t="s">
@@ -8294,10 +8291,10 @@
       <c r="D133" s="1">
         <v>0.09</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E133" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="G133" s="1" t="s">
@@ -8317,10 +8314,10 @@
       <c r="D134" s="1">
         <v>0.09</v>
       </c>
-      <c r="E134" s="2">
+      <c r="E134" s="1">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="G134" s="1" t="s">
@@ -8340,10 +8337,10 @@
       <c r="D135" s="1">
         <v>0.12</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G135" s="1" t="s">
@@ -8363,10 +8360,10 @@
       <c r="D136" s="1">
         <v>0.03</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="1">
         <v>1.0800000000000001E-2</v>
       </c>
       <c r="G136" s="1" t="s">
@@ -8386,10 +8383,10 @@
       <c r="D137" s="1">
         <v>0.12</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G137" s="1" t="s">
@@ -8409,10 +8406,10 @@
       <c r="D138" s="1">
         <v>0.06</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E138" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="1">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="G138" s="1" t="s">
@@ -8432,10 +8429,10 @@
       <c r="D139" s="1">
         <v>0.12</v>
       </c>
-      <c r="E139" s="2">
+      <c r="E139" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G139" s="1" t="s">
@@ -8455,10 +8452,10 @@
       <c r="D140" s="1">
         <v>360</v>
       </c>
-      <c r="E140" s="2">
+      <c r="E140" s="1">
         <v>90</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="1">
         <v>90</v>
       </c>
       <c r="G140" s="1" t="s">
@@ -8478,10 +8475,10 @@
       <c r="D141" s="1">
         <v>36</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="1">
         <v>10.8</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="1">
         <v>10.8</v>
       </c>
       <c r="G141" s="1" t="s">
@@ -8501,10 +8498,10 @@
       <c r="D142" s="1">
         <v>0.18</v>
       </c>
-      <c r="E142" s="2">
+      <c r="E142" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G142" s="1" t="s">
@@ -8524,10 +8521,10 @@
       <c r="D143" s="1">
         <v>0.18</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G143" s="1" t="s">
@@ -8547,10 +8544,10 @@
       <c r="D144" s="1">
         <v>0.216</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="G144" s="1" t="s">
@@ -8570,10 +8567,10 @@
       <c r="D145" s="1">
         <v>0.108</v>
       </c>
-      <c r="E145" s="2">
+      <c r="E145" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="G145" s="1" t="s">
@@ -8593,10 +8590,10 @@
       <c r="D146" s="1">
         <v>0.18</v>
       </c>
-      <c r="E146" s="2">
+      <c r="E146" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="G146" s="1" t="s">
@@ -8616,10 +8613,10 @@
       <c r="D147" s="1">
         <v>0.18</v>
       </c>
-      <c r="E147" s="2">
+      <c r="E147" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G147" s="1" t="s">
@@ -8639,10 +8636,10 @@
       <c r="D148" s="1">
         <v>0.18</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G148" s="1" t="s">
@@ -8662,10 +8659,10 @@
       <c r="D149" s="1">
         <v>0.216</v>
       </c>
-      <c r="E149" s="2">
+      <c r="E149" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="G149" s="1" t="s">
@@ -8685,10 +8682,10 @@
       <c r="D150" s="1">
         <v>0.108</v>
       </c>
-      <c r="E150" s="2">
+      <c r="E150" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="G150" s="1" t="s">
@@ -8708,10 +8705,10 @@
       <c r="D151" s="1">
         <v>0.18</v>
       </c>
-      <c r="E151" s="2">
+      <c r="E151" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="G151" s="1" t="s">
@@ -8731,10 +8728,10 @@
       <c r="D152" s="1">
         <v>0.216</v>
       </c>
-      <c r="E152" s="2">
+      <c r="E152" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="G152" s="1" t="s">
@@ -8754,10 +8751,10 @@
       <c r="D153" s="1">
         <v>180</v>
       </c>
-      <c r="E153" s="2">
+      <c r="E153" s="1">
         <v>34.5</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="1">
         <v>52</v>
       </c>
       <c r="G153" s="1" t="s">
@@ -8777,10 +8774,10 @@
       <c r="D154" s="1">
         <v>18</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>4.5</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>6.5</v>
       </c>
       <c r="G154" s="1" t="s">
@@ -8800,10 +8797,10 @@
       <c r="D155" s="1">
         <v>18</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>4.5</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="1">
         <v>6.5</v>
       </c>
       <c r="G155" s="1" t="s">
@@ -8823,10 +8820,10 @@
       <c r="D156" s="1">
         <v>0.108</v>
       </c>
-      <c r="E156" s="2">
+      <c r="E156" s="1">
         <v>2.3E-2</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="1">
         <v>3.4599999999999999E-2</v>
       </c>
       <c r="G156" s="1" t="s">
@@ -8846,10 +8843,10 @@
       <c r="D157" s="1">
         <v>0.108</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>2.3E-2</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="1">
         <v>3.4599999999999999E-2</v>
       </c>
       <c r="G157" s="1" t="s">
@@ -8869,10 +8866,10 @@
       <c r="D158" s="1">
         <v>0.14399999999999999</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="G158" s="1" t="s">
@@ -8892,10 +8889,10 @@
       <c r="D159" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>8.6E-3</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G159" s="1" t="s">
@@ -8915,10 +8912,10 @@
       <c r="D160" s="1">
         <v>0.14399999999999999</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="G160" s="1" t="s">
@@ -8938,10 +8935,10 @@
       <c r="D161" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>1.44E-2</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="1">
         <v>2.1600000000000001E-2</v>
       </c>
       <c r="G161" s="1" t="s">
@@ -8961,10 +8958,10 @@
       <c r="D162" s="1">
         <v>0.14399999999999999</v>
       </c>
-      <c r="E162" s="2">
+      <c r="E162" s="1">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="1">
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="G162" s="1" t="s">
@@ -8984,10 +8981,10 @@
       <c r="D163" s="1">
         <v>430</v>
       </c>
-      <c r="E163" s="2">
+      <c r="E163" s="1">
         <v>107.5</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="1">
         <v>107.5</v>
       </c>
       <c r="G163" s="1" t="s">
@@ -9007,10 +9004,10 @@
       <c r="D164" s="1">
         <v>43</v>
       </c>
-      <c r="E164" s="2">
+      <c r="E164" s="1">
         <v>12.9</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="1">
         <v>12.9</v>
       </c>
       <c r="G164" s="1" t="s">
@@ -9030,10 +9027,10 @@
       <c r="D165" s="1">
         <v>0.215</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G165" s="1" t="s">
@@ -9053,10 +9050,10 @@
       <c r="D166" s="1">
         <v>0.215</v>
       </c>
-      <c r="E166" s="2">
+      <c r="E166" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G166" s="1" t="s">
@@ -9076,10 +9073,10 @@
       <c r="D167" s="1">
         <v>0.25800000000000001</v>
       </c>
-      <c r="E167" s="2">
+      <c r="E167" s="1">
         <v>5.16E-2</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="1">
         <v>5.16E-2</v>
       </c>
       <c r="G167" s="1" t="s">
@@ -9099,10 +9096,10 @@
       <c r="D168" s="1">
         <v>0.129</v>
       </c>
-      <c r="E168" s="2">
+      <c r="E168" s="1">
         <v>3.44E-2</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="1">
         <v>3.44E-2</v>
       </c>
       <c r="G168" s="1" t="s">
@@ -9122,10 +9119,10 @@
       <c r="D169" s="1">
         <v>0.215</v>
       </c>
-      <c r="E169" s="2">
+      <c r="E169" s="1">
         <v>5.16E-2</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="1">
         <v>5.16E-2</v>
       </c>
       <c r="G169" s="1" t="s">
@@ -9145,10 +9142,10 @@
       <c r="D170" s="1">
         <v>0.215</v>
       </c>
-      <c r="E170" s="2">
+      <c r="E170" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G170" s="1" t="s">
@@ -9168,10 +9165,10 @@
       <c r="D171" s="1">
         <v>0.215</v>
       </c>
-      <c r="E171" s="2">
+      <c r="E171" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G171" s="1" t="s">
@@ -9191,10 +9188,10 @@
       <c r="D172" s="1">
         <v>0.25800000000000001</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>5.16E-2</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="1">
         <v>5.16E-2</v>
       </c>
       <c r="G172" s="1" t="s">
@@ -9214,10 +9211,10 @@
       <c r="D173" s="1">
         <v>0.129</v>
       </c>
-      <c r="E173" s="2">
+      <c r="E173" s="1">
         <v>3.44E-2</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="1">
         <v>3.44E-2</v>
       </c>
       <c r="G173" s="1" t="s">
@@ -9237,10 +9234,10 @@
       <c r="D174" s="1">
         <v>0.215</v>
       </c>
-      <c r="E174" s="2">
+      <c r="E174" s="1">
         <v>5.16E-2</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="1">
         <v>5.16E-2</v>
       </c>
       <c r="G174" s="1" t="s">
@@ -9260,10 +9257,10 @@
       <c r="D175" s="1">
         <v>0.25800000000000001</v>
       </c>
-      <c r="E175" s="2">
+      <c r="E175" s="1">
         <v>5.16E-2</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="1">
         <v>5.16E-2</v>
       </c>
       <c r="G175" s="1" t="s">
@@ -9283,10 +9280,10 @@
       <c r="D176" s="1">
         <v>215</v>
       </c>
-      <c r="E176" s="2">
+      <c r="E176" s="1">
         <v>41.5</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="1">
         <v>62</v>
       </c>
       <c r="G176" s="1" t="s">
@@ -9306,10 +9303,10 @@
       <c r="D177" s="1">
         <v>21.5</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>5</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="1">
         <v>7.5</v>
       </c>
       <c r="G177" s="1" t="s">
@@ -9329,10 +9326,10 @@
       <c r="D178" s="1">
         <v>21.5</v>
       </c>
-      <c r="E178" s="2">
+      <c r="E178" s="1">
         <v>5</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="1">
         <v>7.5</v>
       </c>
       <c r="G178" s="1" t="s">
@@ -9352,10 +9349,10 @@
       <c r="D179" s="1">
         <v>0.129</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>2.75E-2</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="1">
         <v>4.1300000000000003E-2</v>
       </c>
       <c r="G179" s="1" t="s">
@@ -9375,10 +9372,10 @@
       <c r="D180" s="1">
         <v>0.129</v>
       </c>
-      <c r="E180" s="2">
+      <c r="E180" s="1">
         <v>2.75E-2</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="1">
         <v>4.1300000000000003E-2</v>
       </c>
       <c r="G180" s="1" t="s">
@@ -9398,10 +9395,10 @@
       <c r="D181" s="1">
         <v>0.17199999999999999</v>
       </c>
-      <c r="E181" s="2">
+      <c r="E181" s="1">
         <v>3.44E-2</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="1">
         <v>5.16E-2</v>
       </c>
       <c r="G181" s="1" t="s">
@@ -9421,10 +9418,10 @@
       <c r="D182" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="E182" s="2">
+      <c r="E182" s="1">
         <v>1.03E-2</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="1">
         <v>1.55E-2</v>
       </c>
       <c r="G182" s="1" t="s">
@@ -9444,10 +9441,10 @@
       <c r="D183" s="1">
         <v>0.17199999999999999</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>3.44E-2</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="1">
         <v>5.16E-2</v>
       </c>
       <c r="G183" s="1" t="s">
@@ -9467,10 +9464,10 @@
       <c r="D184" s="1">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>1.72E-2</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="1">
         <v>2.58E-2</v>
       </c>
       <c r="G184" s="1" t="s">
@@ -9490,10 +9487,10 @@
       <c r="D185" s="1">
         <v>0.17199999999999999</v>
       </c>
-      <c r="E185" s="2">
+      <c r="E185" s="1">
         <v>3.44E-2</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="1">
         <v>5.16E-2</v>
       </c>
       <c r="G185" s="1" t="s">
@@ -9513,10 +9510,10 @@
       <c r="D186" s="1">
         <v>500</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>125</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="1">
         <v>125</v>
       </c>
       <c r="G186" s="1" t="s">
@@ -9536,10 +9533,10 @@
       <c r="D187" s="1">
         <v>50</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>15</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="1">
         <v>15</v>
       </c>
       <c r="G187" s="1" t="s">
@@ -9559,10 +9556,10 @@
       <c r="D188" s="1">
         <v>0.25</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>0.05</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="1">
         <v>0.05</v>
       </c>
       <c r="G188" s="1" t="s">
@@ -9582,10 +9579,10 @@
       <c r="D189" s="1">
         <v>0.25</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>0.05</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="1">
         <v>0.05</v>
       </c>
       <c r="G189" s="1" t="s">
@@ -9605,10 +9602,10 @@
       <c r="D190" s="1">
         <v>0.3</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>0.06</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="1">
         <v>0.06</v>
       </c>
       <c r="G190" s="1" t="s">
@@ -9628,10 +9625,10 @@
       <c r="D191" s="1">
         <v>0.15</v>
       </c>
-      <c r="E191" s="2">
+      <c r="E191" s="1">
         <v>0.04</v>
       </c>
-      <c r="F191" s="2">
+      <c r="F191" s="1">
         <v>0.04</v>
       </c>
       <c r="G191" s="1" t="s">
@@ -9651,10 +9648,10 @@
       <c r="D192" s="1">
         <v>0.25</v>
       </c>
-      <c r="E192" s="2">
+      <c r="E192" s="1">
         <v>0.06</v>
       </c>
-      <c r="F192" s="2">
+      <c r="F192" s="1">
         <v>0.06</v>
       </c>
       <c r="G192" s="1" t="s">
@@ -9674,10 +9671,10 @@
       <c r="D193" s="1">
         <v>0.25</v>
       </c>
-      <c r="E193" s="2">
+      <c r="E193" s="1">
         <v>0.05</v>
       </c>
-      <c r="F193" s="2">
+      <c r="F193" s="1">
         <v>0.05</v>
       </c>
       <c r="G193" s="1" t="s">
@@ -9697,10 +9694,10 @@
       <c r="D194" s="1">
         <v>0.25</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>0.05</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="1">
         <v>0.05</v>
       </c>
       <c r="G194" s="1" t="s">
@@ -9720,10 +9717,10 @@
       <c r="D195" s="1">
         <v>0.3</v>
       </c>
-      <c r="E195" s="2">
+      <c r="E195" s="1">
         <v>0.06</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="1">
         <v>0.06</v>
       </c>
       <c r="G195" s="1" t="s">
@@ -9743,10 +9740,10 @@
       <c r="D196" s="1">
         <v>0.15</v>
       </c>
-      <c r="E196" s="2">
+      <c r="E196" s="1">
         <v>0.04</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="1">
         <v>0.04</v>
       </c>
       <c r="G196" s="1" t="s">
@@ -9766,10 +9763,10 @@
       <c r="D197" s="1">
         <v>0.25</v>
       </c>
-      <c r="E197" s="2">
+      <c r="E197" s="1">
         <v>0.06</v>
       </c>
-      <c r="F197" s="2">
+      <c r="F197" s="1">
         <v>0.06</v>
       </c>
       <c r="G197" s="1" t="s">
@@ -9789,10 +9786,10 @@
       <c r="D198" s="1">
         <v>0.3</v>
       </c>
-      <c r="E198" s="2">
+      <c r="E198" s="1">
         <v>0.06</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="1">
         <v>0.06</v>
       </c>
       <c r="G198" s="1" t="s">
@@ -9812,10 +9809,10 @@
       <c r="D199" s="1">
         <v>250</v>
       </c>
-      <c r="E199" s="2">
+      <c r="E199" s="1">
         <v>48</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="1">
         <v>72</v>
       </c>
       <c r="G199" s="1" t="s">
@@ -9835,10 +9832,10 @@
       <c r="D200" s="1">
         <v>25</v>
       </c>
-      <c r="E200" s="2">
+      <c r="E200" s="1">
         <v>6</v>
       </c>
-      <c r="F200" s="2">
+      <c r="F200" s="1">
         <v>9</v>
       </c>
       <c r="G200" s="1" t="s">
@@ -9858,10 +9855,10 @@
       <c r="D201" s="1">
         <v>25</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>6</v>
       </c>
-      <c r="F201" s="2">
+      <c r="F201" s="1">
         <v>9</v>
       </c>
       <c r="G201" s="1" t="s">
@@ -9881,10 +9878,10 @@
       <c r="D202" s="1">
         <v>0.15</v>
       </c>
-      <c r="E202" s="2">
+      <c r="E202" s="1">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F202" s="2">
+      <c r="F202" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G202" s="1" t="s">
@@ -9904,10 +9901,10 @@
       <c r="D203" s="1">
         <v>0.15</v>
       </c>
-      <c r="E203" s="2">
+      <c r="E203" s="1">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F203" s="2">
+      <c r="F203" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G203" s="1" t="s">
@@ -9927,10 +9924,10 @@
       <c r="D204" s="1">
         <v>0.2</v>
       </c>
-      <c r="E204" s="2">
+      <c r="E204" s="1">
         <v>0.04</v>
       </c>
-      <c r="F204" s="2">
+      <c r="F204" s="1">
         <v>0.06</v>
       </c>
       <c r="G204" s="1" t="s">
@@ -9950,10 +9947,10 @@
       <c r="D205" s="1">
         <v>0.05</v>
       </c>
-      <c r="E205" s="2">
+      <c r="E205" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="1">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="G205" s="1" t="s">
@@ -9973,10 +9970,10 @@
       <c r="D206" s="1">
         <v>0.2</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>0.04</v>
       </c>
-      <c r="F206" s="2">
+      <c r="F206" s="1">
         <v>0.06</v>
       </c>
       <c r="G206" s="1" t="s">
@@ -9996,10 +9993,10 @@
       <c r="D207" s="1">
         <v>0.1</v>
       </c>
-      <c r="E207" s="2">
+      <c r="E207" s="1">
         <v>0.02</v>
       </c>
-      <c r="F207" s="2">
+      <c r="F207" s="1">
         <v>0.03</v>
       </c>
       <c r="G207" s="1" t="s">
@@ -10019,10 +10016,10 @@
       <c r="D208" s="1">
         <v>0.2</v>
       </c>
-      <c r="E208" s="2">
+      <c r="E208" s="1">
         <v>0.04</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="1">
         <v>0.06</v>
       </c>
       <c r="G208" s="1" t="s">
@@ -10042,10 +10039,10 @@
       <c r="D209" s="1">
         <v>600</v>
       </c>
-      <c r="E209" s="2">
+      <c r="E209" s="1">
         <v>120</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="1">
         <v>180</v>
       </c>
       <c r="G209" s="1" t="s">
@@ -10065,10 +10062,10 @@
       <c r="D210" s="1">
         <v>60</v>
       </c>
-      <c r="E210" s="2">
+      <c r="E210" s="1">
         <v>14.5</v>
       </c>
-      <c r="F210" s="2">
+      <c r="F210" s="1">
         <v>21.5</v>
       </c>
       <c r="G210" s="1" t="s">
@@ -10088,10 +10085,10 @@
       <c r="D211" s="1">
         <v>0.3</v>
       </c>
-      <c r="E211" s="2">
+      <c r="E211" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G211" s="1" t="s">
@@ -10111,10 +10108,10 @@
       <c r="D212" s="1">
         <v>0.3</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G212" s="1" t="s">
@@ -10134,10 +10131,10 @@
       <c r="D213" s="1">
         <v>0.36</v>
       </c>
-      <c r="E213" s="2">
+      <c r="E213" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="1">
         <v>8.6400000000000005E-2</v>
       </c>
       <c r="G213" s="1" t="s">
@@ -10157,10 +10154,10 @@
       <c r="D214" s="1">
         <v>0.18</v>
       </c>
-      <c r="E214" s="2">
+      <c r="E214" s="1">
         <v>3.8399999999999997E-2</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
       <c r="G214" s="1" t="s">
@@ -10180,10 +10177,10 @@
       <c r="D215" s="1">
         <v>0.3</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="1">
         <v>8.6400000000000005E-2</v>
       </c>
       <c r="G215" s="1" t="s">
@@ -10203,10 +10200,10 @@
       <c r="D216" s="1">
         <v>0.3</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F216" s="2">
+      <c r="F216" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G216" s="1" t="s">
@@ -10226,10 +10223,10 @@
       <c r="D217" s="1">
         <v>0.3</v>
       </c>
-      <c r="E217" s="2">
+      <c r="E217" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G217" s="1" t="s">
@@ -10249,10 +10246,10 @@
       <c r="D218" s="1">
         <v>0.36</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="1">
         <v>8.6400000000000005E-2</v>
       </c>
       <c r="G218" s="1" t="s">
@@ -10272,10 +10269,10 @@
       <c r="D219" s="1">
         <v>0.18</v>
       </c>
-      <c r="E219" s="2">
+      <c r="E219" s="1">
         <v>3.8399999999999997E-2</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
       <c r="G219" s="1" t="s">
@@ -10295,10 +10292,10 @@
       <c r="D220" s="1">
         <v>0.3</v>
       </c>
-      <c r="E220" s="2">
+      <c r="E220" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="1">
         <v>8.6400000000000005E-2</v>
       </c>
       <c r="G220" s="1" t="s">
@@ -10318,10 +10315,10 @@
       <c r="D221" s="1">
         <v>0.36</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="1">
         <v>8.6400000000000005E-2</v>
       </c>
       <c r="G221" s="1" t="s">
@@ -10341,10 +10338,10 @@
       <c r="D222" s="1">
         <v>300</v>
       </c>
-      <c r="E222" s="2">
+      <c r="E222" s="1">
         <v>57.5</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="1">
         <v>86.5</v>
       </c>
       <c r="G222" s="1" t="s">
@@ -10364,10 +10361,10 @@
       <c r="D223" s="1">
         <v>30</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>7</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="1">
         <v>11</v>
       </c>
       <c r="G223" s="1" t="s">
@@ -10387,10 +10384,10 @@
       <c r="D224" s="1">
         <v>30</v>
       </c>
-      <c r="E224" s="2">
+      <c r="E224" s="1">
         <v>7</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="1">
         <v>11</v>
       </c>
       <c r="G224" s="1" t="s">
@@ -10410,10 +10407,10 @@
       <c r="D225" s="1">
         <v>0.18</v>
       </c>
-      <c r="E225" s="2">
+      <c r="E225" s="1">
         <v>3.8399999999999997E-2</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
       <c r="G225" s="1" t="s">
@@ -10433,10 +10430,10 @@
       <c r="D226" s="1">
         <v>0.18</v>
       </c>
-      <c r="E226" s="2">
+      <c r="E226" s="1">
         <v>3.8399999999999997E-2</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="1">
         <v>5.7599999999999998E-2</v>
       </c>
       <c r="G226" s="1" t="s">
@@ -10456,10 +10453,10 @@
       <c r="D227" s="1">
         <v>0.24</v>
       </c>
-      <c r="E227" s="2">
+      <c r="E227" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G227" s="1" t="s">
@@ -10479,10 +10476,10 @@
       <c r="D228" s="1">
         <v>0.06</v>
       </c>
-      <c r="E228" s="2">
+      <c r="E228" s="1">
         <v>1.44E-2</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="1">
         <v>2.1600000000000001E-2</v>
       </c>
       <c r="G228" s="1" t="s">
@@ -10502,10 +10499,10 @@
       <c r="D229" s="1">
         <v>0.24</v>
       </c>
-      <c r="E229" s="2">
+      <c r="E229" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G229" s="1" t="s">
@@ -10525,10 +10522,10 @@
       <c r="D230" s="1">
         <v>0.12</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="1">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G230" s="1" t="s">
@@ -10548,10 +10545,10 @@
       <c r="D231" s="1">
         <v>0.24</v>
       </c>
-      <c r="E231" s="2">
+      <c r="E231" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G231" s="1" t="s">

--- a/Assets/ExcelData/ItemTable.xlsx
+++ b/Assets/ExcelData/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1CA696-5111-450E-BC28-7F9A01304FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB11863-C6A6-4A51-A04A-96EF1CA53268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8355" yWindow="2685" windowWidth="21600" windowHeight="11385" tabRatio="791" activeTab="7" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="791" xr2:uid="{79C10FCB-8206-4E1E-8455-B9F6861255DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="1" r:id="rId1"/>
@@ -1614,7 +1614,7 @@
     <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="32.75" customWidth="1"/>
     <col min="3" max="3" width="17.25" customWidth="1"/>
-    <col min="4" max="4" width="31.875" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.625" customWidth="1"/>
     <col min="7" max="7" width="22.375" customWidth="1"/>
     <col min="8" max="8" width="24.75" customWidth="1"/>
